--- a/macroeconomic_data/NGX_Macro_project_data(complete).xlsx
+++ b/macroeconomic_data/NGX_Macro_project_data(complete).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\Nigerian_Macroeconomic_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{671A7913-EA6E-4991-972A-33449B47495B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4C19EFD-6798-4978-BC48-6C838CFCD007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D2B570D0-6D1A-471A-AABF-57B2DA6530E5}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>month_idx</t>
   </si>
   <si>
-    <t>consumer_price_index(CPI)</t>
-  </si>
-  <si>
     <t>112.63</t>
   </si>
   <si>
@@ -749,18 +746,6 @@
     <t>1.84</t>
   </si>
   <si>
-    <t>Crude Oil Price</t>
-  </si>
-  <si>
-    <t>Domestic Production</t>
-  </si>
-  <si>
-    <t>Crude Oil Export</t>
-  </si>
-  <si>
-    <t>Inflation_allItemsAverage</t>
-  </si>
-  <si>
     <t>17.63</t>
   </si>
   <si>
@@ -1406,9 +1391,6 @@
     <t>23096526.55</t>
   </si>
   <si>
-    <t>Money Supply(M2)</t>
-  </si>
-  <si>
     <t>5689981.32</t>
   </si>
   <si>
@@ -2081,12 +2063,6 @@
     <t>3311609.44</t>
   </si>
   <si>
-    <t>bank reserves</t>
-  </si>
-  <si>
-    <t>currency in circulation</t>
-  </si>
-  <si>
     <t>26951480.44</t>
   </si>
   <si>
@@ -3092,18 +3068,6 @@
     <t>26508030.42</t>
   </si>
   <si>
-    <t>netForeignAssets</t>
-  </si>
-  <si>
-    <t>netDomesticAssets</t>
-  </si>
-  <si>
-    <t>netDomesticCredit</t>
-  </si>
-  <si>
-    <t>creditToGovernment</t>
-  </si>
-  <si>
     <t>40378881.21</t>
   </si>
   <si>
@@ -3440,9 +3404,6 @@
     <t>4629967.24</t>
   </si>
   <si>
-    <t>creditToPrivateSector</t>
-  </si>
-  <si>
     <t>81041509.68</t>
   </si>
   <si>
@@ -4073,24 +4034,9 @@
     <t>13.75</t>
   </si>
   <si>
-    <t>MonetaryPolicyRate</t>
-  </si>
-  <si>
-    <t>TreasuryBillRate</t>
-  </si>
-  <si>
-    <t>Lending_Rate</t>
-  </si>
-  <si>
     <t>19.10</t>
   </si>
   <si>
-    <t>Exchange_Rate(USD-EOP)</t>
-  </si>
-  <si>
-    <t>Premium_Motor_Spirit(PMS)</t>
-  </si>
-  <si>
     <t>145</t>
   </si>
   <si>
@@ -4277,177 +4223,6 @@
     <t>897</t>
   </si>
   <si>
-    <t>GDP at Current Basic Prices</t>
-  </si>
-  <si>
-    <t>Net Taxes on Products</t>
-  </si>
-  <si>
-    <t>GDP at Current Market Prices</t>
-  </si>
-  <si>
-    <t>gdp_ind_MQ_Crude Petroleum and Natural Gas</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> gdp_Fishing</t>
-  </si>
-  <si>
-    <t>gdp_agric_Forestry</t>
-  </si>
-  <si>
-    <t>gdp_agric_Livestock</t>
-  </si>
-  <si>
-    <t>gdp_agric_Crop Production</t>
-  </si>
-  <si>
-    <t>gdp_ind_Mining and Quarrying(MQ)</t>
-  </si>
-  <si>
-    <t>GDP_INDUSTRY(ind)</t>
-  </si>
-  <si>
-    <t>A. GDP_AGRICULTURE(agric)</t>
-  </si>
-  <si>
-    <t>gdp_ind_MQ_Coal Mining</t>
-  </si>
-  <si>
-    <t>gdp_ind_MQ_Metal Ores</t>
-  </si>
-  <si>
-    <t>gdp_ind_MQ_Quarrying and Other Minerals</t>
-  </si>
-  <si>
-    <t>gdp_ind_Manufacturing(mfg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> gdp_ind_mfg_Oil Refining</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Cement</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Food, Beverage and Tobacco</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Textile, Apparel and Footwear</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Wood and Wood Products</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Pulp, Paper and Paper Products</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Chemical and Pharmaceutical Products</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Non-Metallic Products</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Plastic and Rubber Products</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Electrical and Electronics</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Basic Metal, Iron and Steel</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Motor Vehicles and Assembly</t>
-  </si>
-  <si>
-    <t>gdp_ind_mfg_Other Manufacturing</t>
-  </si>
-  <si>
-    <t>gdp_ind_Electricity, Gas, Steam &amp; Air conditioner</t>
-  </si>
-  <si>
-    <t>gdp_ind_Construction</t>
-  </si>
-  <si>
-    <t>gdp_ind_Water supply, Sewage, Waste Management</t>
-  </si>
-  <si>
-    <t>GDP_SERVICES(svc)</t>
-  </si>
-  <si>
-    <t>gdp_svc_Trade</t>
-  </si>
-  <si>
-    <t>gdp_svc_Accommodation and Food Services</t>
-  </si>
-  <si>
-    <t>gdp_svc_Transportation and Storage(TS)</t>
-  </si>
-  <si>
-    <t>gdp_svc_TS_RoadTransport</t>
-  </si>
-  <si>
-    <t>gdp_svc_TS_Rail Transport &amp; Pipelines</t>
-  </si>
-  <si>
-    <t>gdp_svc_TS_Water Transport</t>
-  </si>
-  <si>
-    <t>gdp_svc_TS_Air Transport</t>
-  </si>
-  <si>
-    <t>gdp_svc_TS_Transport Services</t>
-  </si>
-  <si>
-    <t>gdp_svc_TS_Post and Courier Services</t>
-  </si>
-  <si>
-    <t>gdp_svc_Information and Communication(IC)</t>
-  </si>
-  <si>
-    <t>gdp_svc_IC_Telecommunications and Information Services</t>
-  </si>
-  <si>
-    <t>gdp_svc_IC_Publishing</t>
-  </si>
-  <si>
-    <t>gdp_svc_IC_Motion Pictures, Sound Recording and Music Production</t>
-  </si>
-  <si>
-    <t>gdp_svc_IC_Broadcasting</t>
-  </si>
-  <si>
-    <t>gdp_svc_Arts, Entertainment &amp; Recreation</t>
-  </si>
-  <si>
-    <t>gdp_svc_Financial and Insurance(FI)</t>
-  </si>
-  <si>
-    <t>gdp_svc_FI_Financial Institutions</t>
-  </si>
-  <si>
-    <t>gdp_svc_FI_Insurance</t>
-  </si>
-  <si>
-    <t>gdp_svc_Real Estate</t>
-  </si>
-  <si>
-    <t>gdp_svc_Professional, Scientific &amp; Technical Services</t>
-  </si>
-  <si>
-    <t>gdp_svc_Administrative and Support Services</t>
-  </si>
-  <si>
-    <t>gdp_svc_Public Administration</t>
-  </si>
-  <si>
-    <t>gdp_svc_Education</t>
-  </si>
-  <si>
-    <t>gdp_svc_Human Health &amp; Social Services</t>
-  </si>
-  <si>
-    <t>gdp_svc_Other Services</t>
-  </si>
-  <si>
     <t>01/31/2017</t>
   </si>
   <si>
@@ -4796,10 +4571,235 @@
     <t>FR_Date</t>
   </si>
   <si>
-    <t>foreign_reserve_Gross(USD)</t>
-  </si>
-  <si>
-    <t>foreign_reserve_Liquid(USD)</t>
+    <t>consumer_price_index(CPI)_monthly</t>
+  </si>
+  <si>
+    <t>Crude Oil Price_monthly</t>
+  </si>
+  <si>
+    <t>Domestic Production_monthly</t>
+  </si>
+  <si>
+    <t>Crude Oil Export_monthly</t>
+  </si>
+  <si>
+    <t>Inflation_allItemsAverage_monthly</t>
+  </si>
+  <si>
+    <t>Money Supply(M2)_monthly</t>
+  </si>
+  <si>
+    <t>currency in circulation_monthly</t>
+  </si>
+  <si>
+    <t>bank reserves_monthly</t>
+  </si>
+  <si>
+    <t>netForeignAssets_monthly</t>
+  </si>
+  <si>
+    <t>netDomesticAssets_monthly</t>
+  </si>
+  <si>
+    <t>netDomesticCredit_monthly</t>
+  </si>
+  <si>
+    <t>creditToGovernment_monthly</t>
+  </si>
+  <si>
+    <t>creditToPrivateSector_monthly</t>
+  </si>
+  <si>
+    <t>MonetaryPolicyRate_monthly</t>
+  </si>
+  <si>
+    <t>TreasuryBillRate_monthly</t>
+  </si>
+  <si>
+    <t>Lending_Rate_monthly</t>
+  </si>
+  <si>
+    <t>Exchange_Rate(USD-EOP)_monthly</t>
+  </si>
+  <si>
+    <t>Premium_Motor_Spirit(PMS)_monthly</t>
+  </si>
+  <si>
+    <t>A. GDP_AGRICULTURE(agric)_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_agric_Crop Production_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_agric_Livestock_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_agric_Forestry_quarterly</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> gdp_Fishing_quarterly</t>
+  </si>
+  <si>
+    <t>GDP_INDUSTRY(ind)_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_Mining and Quarrying(MQ)_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_MQ_Crude Petroleum and Natural Gas_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_MQ_Coal Mining_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_MQ_Metal Ores_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_MQ_Quarrying and Other Minerals_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_Manufacturing(mfg)_quarterly</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> gdp_ind_mfg_Oil Refining_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Cement_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Food, Beverage and Tobacco_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Textile, Apparel and Footwear_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Wood and Wood Products_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Pulp, Paper and Paper Products_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Chemical and Pharmaceutical Products_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Non-Metallic Products_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Plastic and Rubber Products_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Electrical and Electronics_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Basic Metal, Iron and Steel_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Motor Vehicles and Assembly_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_mfg_Other Manufacturing_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_Electricity, Gas, Steam &amp; Air conditioner_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_Water supply, Sewage, Waste Management_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_ind_Construction_quarterly</t>
+  </si>
+  <si>
+    <t>GDP_SERVICES(svc)_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Trade_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Accommodation and Food Services_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Transportation and Storage(TS)_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_TS_RoadTransport_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_TS_Rail Transport &amp; Pipelines_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_TS_Water Transport_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_TS_Air Transport_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_TS_Transport Services_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_TS_Post and Courier Services_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Information and Communication(IC)_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_IC_Telecommunications and Information Services_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_IC_Publishing_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_IC_Motion Pictures, Sound Recording and Music Production_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_IC_Broadcasting_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Arts, Entertainment &amp; Recreation_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Financial and Insurance(FI)_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_FI_Financial Institutions_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_FI_Insurance_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Real Estate_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Professional, Scientific &amp; Technical Services_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Administrative and Support Services_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Public Administration_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Education_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Human Health &amp; Social Services_quarterly</t>
+  </si>
+  <si>
+    <t>gdp_svc_Other Services_quarterly</t>
+  </si>
+  <si>
+    <t>GDP at Current Basic Prices_quarterly</t>
+  </si>
+  <si>
+    <t>Net Taxes on Products_quarterly</t>
+  </si>
+  <si>
+    <t>GDP at Current Market Prices_quarterly</t>
+  </si>
+  <si>
+    <t>foreign_reserve_Gross(USD)_monthly</t>
+  </si>
+  <si>
+    <t>foreign_reserve_Liquid(USD)_monthly</t>
   </si>
 </sst>
 </file>
@@ -5301,85 +5301,87 @@
   <dimension ref="A1:EA121"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="29.08984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="39" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="21.6328125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="24" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="35.81640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="37.54296875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="44.26953125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="34.81640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="32.54296875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="35.6328125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="40.36328125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="36.81640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="31.6328125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="26.08984375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="37.6328125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="48.54296875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="56.36328125" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="35.08984375" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="30.36328125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="44.1796875" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="37.54296875" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="34.1796875" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="31.54296875" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="33.26953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30.90625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="47.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="43.6328125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="43.36328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="44" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="40.90625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="45.7265625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="38.26953125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="43" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="40.7265625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="43.81640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="36.81640625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="48.54296875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="51.26953125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="45" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="41.7265625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="31.08984375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="39.81640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="34.26953125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="40" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="45.81640625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="56.7265625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="64.54296875" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="43.26953125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="38.54296875" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="35.7265625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="52.36328125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="45.7265625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="33.81640625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="42.36328125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="32.90625" bestFit="1" customWidth="1"/>
     <col min="79" max="79" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="31.26953125" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="31.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:131" ht="16" x14ac:dyDescent="0.4">
@@ -5393,232 +5395,232 @@
         <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>1510</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>236</v>
+        <v>1511</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>237</v>
+        <v>1512</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>238</v>
+        <v>1513</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>239</v>
+        <v>1514</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>455</v>
+        <v>1515</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>681</v>
+        <v>1516</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>680</v>
+        <v>1517</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>1017</v>
+        <v>1518</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>1018</v>
+        <v>1519</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>1019</v>
+        <v>1520</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>1020</v>
+        <v>1521</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>1133</v>
+        <v>1522</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>1344</v>
+        <v>1523</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>1345</v>
+        <v>1524</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>1346</v>
+        <v>1525</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>1348</v>
+        <v>1526</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>1349</v>
+        <v>1527</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>1422</v>
+        <v>1528</v>
       </c>
       <c r="W1" t="s">
-        <v>1419</v>
+        <v>1529</v>
       </c>
       <c r="X1" t="s">
-        <v>1418</v>
+        <v>1530</v>
       </c>
       <c r="Y1" t="s">
-        <v>1417</v>
+        <v>1531</v>
       </c>
       <c r="Z1" t="s">
-        <v>1416</v>
+        <v>1532</v>
       </c>
       <c r="AA1" t="s">
-        <v>1421</v>
+        <v>1533</v>
       </c>
       <c r="AB1" t="s">
-        <v>1420</v>
+        <v>1534</v>
       </c>
       <c r="AC1" t="s">
-        <v>1415</v>
+        <v>1535</v>
       </c>
       <c r="AD1" t="s">
-        <v>1423</v>
+        <v>1536</v>
       </c>
       <c r="AE1" t="s">
-        <v>1424</v>
+        <v>1537</v>
       </c>
       <c r="AF1" t="s">
-        <v>1425</v>
+        <v>1538</v>
       </c>
       <c r="AG1" t="s">
-        <v>1426</v>
+        <v>1539</v>
       </c>
       <c r="AH1" t="s">
-        <v>1427</v>
+        <v>1540</v>
       </c>
       <c r="AI1" t="s">
-        <v>1428</v>
+        <v>1541</v>
       </c>
       <c r="AJ1" t="s">
-        <v>1429</v>
+        <v>1542</v>
       </c>
       <c r="AK1" t="s">
-        <v>1430</v>
+        <v>1543</v>
       </c>
       <c r="AL1" t="s">
-        <v>1431</v>
+        <v>1544</v>
       </c>
       <c r="AM1" t="s">
-        <v>1432</v>
+        <v>1545</v>
       </c>
       <c r="AN1" t="s">
-        <v>1433</v>
+        <v>1546</v>
       </c>
       <c r="AO1" t="s">
-        <v>1434</v>
+        <v>1547</v>
       </c>
       <c r="AP1" t="s">
-        <v>1435</v>
+        <v>1548</v>
       </c>
       <c r="AQ1" t="s">
-        <v>1436</v>
+        <v>1549</v>
       </c>
       <c r="AR1" t="s">
-        <v>1437</v>
+        <v>1550</v>
       </c>
       <c r="AS1" t="s">
-        <v>1438</v>
+        <v>1551</v>
       </c>
       <c r="AT1" t="s">
-        <v>1439</v>
+        <v>1552</v>
       </c>
       <c r="AU1" t="s">
-        <v>1440</v>
+        <v>1553</v>
       </c>
       <c r="AV1" t="s">
-        <v>1442</v>
+        <v>1554</v>
       </c>
       <c r="AW1" t="s">
-        <v>1441</v>
+        <v>1555</v>
       </c>
       <c r="AX1" t="s">
-        <v>1443</v>
+        <v>1556</v>
       </c>
       <c r="AY1" t="s">
-        <v>1444</v>
+        <v>1557</v>
       </c>
       <c r="AZ1" t="s">
-        <v>1445</v>
+        <v>1558</v>
       </c>
       <c r="BA1" t="s">
-        <v>1446</v>
+        <v>1559</v>
       </c>
       <c r="BB1" t="s">
-        <v>1447</v>
+        <v>1560</v>
       </c>
       <c r="BC1" t="s">
-        <v>1448</v>
+        <v>1561</v>
       </c>
       <c r="BD1" t="s">
-        <v>1449</v>
+        <v>1562</v>
       </c>
       <c r="BE1" t="s">
-        <v>1450</v>
+        <v>1563</v>
       </c>
       <c r="BF1" t="s">
-        <v>1451</v>
+        <v>1564</v>
       </c>
       <c r="BG1" t="s">
-        <v>1452</v>
+        <v>1565</v>
       </c>
       <c r="BH1" t="s">
-        <v>1453</v>
+        <v>1566</v>
       </c>
       <c r="BI1" t="s">
-        <v>1454</v>
+        <v>1567</v>
       </c>
       <c r="BJ1" t="s">
-        <v>1455</v>
+        <v>1568</v>
       </c>
       <c r="BK1" t="s">
-        <v>1456</v>
+        <v>1569</v>
       </c>
       <c r="BL1" t="s">
-        <v>1457</v>
+        <v>1570</v>
       </c>
       <c r="BM1" t="s">
-        <v>1458</v>
+        <v>1571</v>
       </c>
       <c r="BN1" t="s">
-        <v>1459</v>
+        <v>1572</v>
       </c>
       <c r="BO1" t="s">
-        <v>1460</v>
+        <v>1573</v>
       </c>
       <c r="BP1" t="s">
-        <v>1461</v>
+        <v>1574</v>
       </c>
       <c r="BQ1" t="s">
-        <v>1462</v>
+        <v>1575</v>
       </c>
       <c r="BR1" t="s">
-        <v>1463</v>
+        <v>1576</v>
       </c>
       <c r="BS1" t="s">
-        <v>1464</v>
+        <v>1577</v>
       </c>
       <c r="BT1" t="s">
-        <v>1465</v>
+        <v>1578</v>
       </c>
       <c r="BU1" t="s">
-        <v>1466</v>
+        <v>1579</v>
       </c>
       <c r="BV1" t="s">
-        <v>1467</v>
+        <v>1580</v>
       </c>
       <c r="BW1" t="s">
-        <v>1468</v>
+        <v>1581</v>
       </c>
       <c r="BX1" t="s">
-        <v>1412</v>
+        <v>1582</v>
       </c>
       <c r="BY1" t="s">
-        <v>1413</v>
+        <v>1583</v>
       </c>
       <c r="BZ1" t="s">
-        <v>1414</v>
+        <v>1584</v>
       </c>
       <c r="CA1" t="s">
-        <v>1584</v>
+        <v>1509</v>
       </c>
       <c r="CB1" t="s">
         <v>1585</v>
@@ -5641,46 +5643,46 @@
         <v>198.04124120608799</v>
       </c>
       <c r="E2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" t="s">
         <v>234</v>
       </c>
-      <c r="F2" t="s">
-        <v>235</v>
-      </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>1132</v>
+        <v>1120</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>1245</v>
+        <v>1232</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="S2">
         <v>16.91</v>
@@ -5689,11 +5691,11 @@
         <v>305.25</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>1350</v>
+        <v>1332</v>
       </c>
       <c r="V2" s="8"/>
       <c r="CA2" t="s">
-        <v>1469</v>
+        <v>1394</v>
       </c>
       <c r="CB2">
         <v>28174226894.439999</v>
@@ -5764,46 +5766,46 @@
         <v>201.00114134919801</v>
       </c>
       <c r="E3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F3" t="s">
         <v>232</v>
       </c>
-      <c r="F3" t="s">
-        <v>233</v>
-      </c>
       <c r="G3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>1244</v>
+        <v>1231</v>
       </c>
       <c r="Q3" s="2">
         <v>14</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>1343</v>
+        <v>1330</v>
       </c>
       <c r="S3">
         <v>17.13</v>
@@ -5812,11 +5814,11 @@
         <v>305.5</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>1350</v>
+        <v>1332</v>
       </c>
       <c r="V3" s="8"/>
       <c r="CA3" t="s">
-        <v>1470</v>
+        <v>1395</v>
       </c>
       <c r="CB3">
         <v>29646676385.389999</v>
@@ -5837,46 +5839,46 @@
         <v>204.456609889438</v>
       </c>
       <c r="E4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" t="s">
         <v>230</v>
       </c>
-      <c r="F4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" t="s">
-        <v>231</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>1130</v>
+        <v>1118</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>1243</v>
+        <v>1230</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>1342</v>
+        <v>1329</v>
       </c>
       <c r="S4">
         <v>17.43</v>
@@ -5885,7 +5887,7 @@
         <v>306.35000000000002</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>1351</v>
+        <v>1333</v>
       </c>
       <c r="V4">
         <v>4686.22</v>
@@ -6059,7 +6061,7 @@
         <v>26228.85</v>
       </c>
       <c r="CA4" t="s">
-        <v>1471</v>
+        <v>1396</v>
       </c>
       <c r="CB4">
         <v>30297945681.580002</v>
@@ -6080,46 +6082,46 @@
         <v>207.72967753369201</v>
       </c>
       <c r="E5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" t="s">
         <v>228</v>
       </c>
-      <c r="F5" t="s">
-        <v>229</v>
-      </c>
       <c r="G5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>1129</v>
+        <v>1117</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>1242</v>
+        <v>1229</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>1341</v>
+        <v>1328</v>
       </c>
       <c r="S5">
         <v>17.440000000000001</v>
@@ -6128,7 +6130,7 @@
         <v>305.85000000000002</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
@@ -6187,7 +6189,7 @@
       <c r="BY5" s="7"/>
       <c r="BZ5" s="7"/>
       <c r="CA5" t="s">
-        <v>1542</v>
+        <v>1467</v>
       </c>
       <c r="CB5">
         <v>30864632988.75</v>
@@ -6208,46 +6210,46 @@
         <v>211.63780921259999</v>
       </c>
       <c r="E6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F6" t="s">
         <v>226</v>
       </c>
-      <c r="F6" t="s">
-        <v>227</v>
-      </c>
       <c r="G6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>1241</v>
+        <v>1228</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="S6">
         <v>17.579999999999998</v>
@@ -6256,7 +6258,7 @@
         <v>305.39999999999998</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>1353</v>
+        <v>1335</v>
       </c>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
@@ -6315,7 +6317,7 @@
       <c r="BY6" s="7"/>
       <c r="BZ6" s="7"/>
       <c r="CA6" t="s">
-        <v>1472</v>
+        <v>1397</v>
       </c>
       <c r="CB6">
         <v>30329636330.560001</v>
@@ -6336,46 +6338,46 @@
         <v>214.982456187374</v>
       </c>
       <c r="E7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" t="s">
         <v>197</v>
       </c>
-      <c r="G7" t="s">
-        <v>198</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1127</v>
+        <v>1115</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>1240</v>
+        <v>1227</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="S7">
         <v>17.59</v>
@@ -6384,7 +6386,7 @@
         <v>305.89999999999998</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>1354</v>
+        <v>1336</v>
       </c>
       <c r="V7">
         <v>5210.1499999999996</v>
@@ -6558,7 +6560,7 @@
         <v>27266.39</v>
       </c>
       <c r="CA7" t="s">
-        <v>1473</v>
+        <v>1398</v>
       </c>
       <c r="CB7">
         <v>30288411299.290001</v>
@@ -6579,46 +6581,46 @@
         <v>217.590466467304</v>
       </c>
       <c r="E8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F8" t="s">
+        <v>203</v>
+      </c>
+      <c r="G8" t="s">
         <v>204</v>
       </c>
-      <c r="G8" t="s">
-        <v>205</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>1239</v>
+        <v>1226</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>1340</v>
+        <v>1327</v>
       </c>
       <c r="S8">
         <v>17.649999999999999</v>
@@ -6627,10 +6629,10 @@
         <v>305.64999999999998</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>1355</v>
+        <v>1337</v>
       </c>
       <c r="CA8" t="s">
-        <v>1474</v>
+        <v>1399</v>
       </c>
       <c r="CB8">
         <v>30843102473.560001</v>
@@ -6651,46 +6653,46 @@
         <v>219.70175256378101</v>
       </c>
       <c r="E9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>1339</v>
+        <v>1326</v>
       </c>
       <c r="S9">
         <v>17.690000000000001</v>
@@ -6699,10 +6701,10 @@
         <v>305.85000000000002</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>1356</v>
+        <v>1338</v>
       </c>
       <c r="CA9" t="s">
-        <v>1475</v>
+        <v>1400</v>
       </c>
       <c r="CB9">
         <v>31825701619.59</v>
@@ -6723,46 +6725,46 @@
         <v>221.42601974703001</v>
       </c>
       <c r="E10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F10" t="s">
         <v>221</v>
       </c>
-      <c r="F10" t="s">
-        <v>222</v>
-      </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>1124</v>
+        <v>1112</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>1237</v>
+        <v>1224</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>1338</v>
+        <v>1325</v>
       </c>
       <c r="S10">
         <v>17.88</v>
@@ -6771,7 +6773,7 @@
         <v>305.75</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>1357</v>
+        <v>1339</v>
       </c>
       <c r="V10">
         <v>7198.21</v>
@@ -6945,7 +6947,7 @@
         <v>29756.01</v>
       </c>
       <c r="CA10" t="s">
-        <v>1543</v>
+        <v>1468</v>
       </c>
       <c r="CB10">
         <v>32490900723.279999</v>
@@ -6966,46 +6968,46 @@
         <v>223.11299263760199</v>
       </c>
       <c r="E11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G11" t="s">
         <v>197</v>
       </c>
-      <c r="G11" t="s">
-        <v>198</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>1123</v>
+        <v>1111</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>1236</v>
+        <v>1223</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>1337</v>
+        <v>1324</v>
       </c>
       <c r="S11">
         <v>17.86</v>
@@ -7014,10 +7016,10 @@
         <v>305.8</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>1358</v>
+        <v>1340</v>
       </c>
       <c r="CA11" t="s">
-        <v>1476</v>
+        <v>1401</v>
       </c>
       <c r="CB11">
         <v>33825011432.470001</v>
@@ -7038,46 +7040,46 @@
         <v>224.85695190601001</v>
       </c>
       <c r="E12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>1122</v>
+        <v>1110</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>1235</v>
+        <v>1222</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>1336</v>
+        <v>1323</v>
       </c>
       <c r="S12">
         <v>17.77</v>
@@ -7086,10 +7088,10 @@
         <v>306</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>1359</v>
+        <v>1341</v>
       </c>
       <c r="CA12" t="s">
-        <v>1477</v>
+        <v>1402</v>
       </c>
       <c r="CB12">
         <v>34945550023.209999</v>
@@ -7110,46 +7112,46 @@
         <v>226.19095663611299</v>
       </c>
       <c r="E13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>1121</v>
+        <v>1109</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>1234</v>
+        <v>1221</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>1327</v>
+        <v>1314</v>
       </c>
       <c r="S13">
         <v>17.71</v>
@@ -7158,7 +7160,7 @@
         <v>306</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>1360</v>
+        <v>1342</v>
       </c>
       <c r="V13">
         <v>6857.98</v>
@@ -7332,7 +7334,7 @@
         <v>31647.99</v>
       </c>
       <c r="CA13" t="s">
-        <v>1544</v>
+        <v>1469</v>
       </c>
       <c r="CB13">
         <v>38765961445.419998</v>
@@ -7355,46 +7357,46 @@
         <v>227.99842953581501</v>
       </c>
       <c r="E14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F14" t="s">
+        <v>207</v>
+      </c>
+      <c r="G14" t="s">
         <v>208</v>
       </c>
-      <c r="G14" t="s">
-        <v>209</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>1233</v>
+        <v>1220</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>1335</v>
+        <v>1322</v>
       </c>
       <c r="S14">
         <v>17.5</v>
@@ -7403,10 +7405,10 @@
         <v>305.7</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>1361</v>
+        <v>1343</v>
       </c>
       <c r="CA14" t="s">
-        <v>1478</v>
+        <v>1403</v>
       </c>
       <c r="CB14">
         <v>40685233207.040001</v>
@@ -7427,46 +7429,46 @@
         <v>229.803827747859</v>
       </c>
       <c r="E15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F15" t="s">
+        <v>203</v>
+      </c>
+      <c r="G15" t="s">
         <v>204</v>
       </c>
-      <c r="G15" t="s">
-        <v>205</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>1232</v>
+        <v>1219</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>1334</v>
+        <v>1321</v>
       </c>
       <c r="S15">
         <v>17.53</v>
@@ -7475,10 +7477,10 @@
         <v>305.89999999999998</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>1362</v>
+        <v>1344</v>
       </c>
       <c r="CA15" t="s">
-        <v>1479</v>
+        <v>1404</v>
       </c>
       <c r="CB15">
         <v>42492668841.440002</v>
@@ -7499,46 +7501,46 @@
         <v>231.72534835952101</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>1231</v>
+        <v>1218</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>1333</v>
+        <v>1320</v>
       </c>
       <c r="S16">
         <v>17.350000000000001</v>
@@ -7547,7 +7549,7 @@
         <v>305.64999999999998</v>
       </c>
       <c r="U16" s="7" t="s">
-        <v>1363</v>
+        <v>1345</v>
       </c>
       <c r="V16">
         <v>4957.8599999999997</v>
@@ -7721,7 +7723,7 @@
         <v>28682.95</v>
       </c>
       <c r="CA16" t="s">
-        <v>1545</v>
+        <v>1470</v>
       </c>
       <c r="CB16">
         <v>46257182160.709999</v>
@@ -7742,46 +7744,46 @@
         <v>233.65920097847999</v>
       </c>
       <c r="E17" t="s">
+        <v>213</v>
+      </c>
+      <c r="F17" t="s">
         <v>214</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>215</v>
       </c>
-      <c r="G17" t="s">
-        <v>216</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>1230</v>
+        <v>1217</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>1332</v>
+        <v>1319</v>
       </c>
       <c r="S17">
         <v>17.239999999999998</v>
@@ -7790,10 +7792,10 @@
         <v>305.7</v>
       </c>
       <c r="U17" s="7" t="s">
-        <v>1364</v>
+        <v>1346</v>
       </c>
       <c r="CA17" t="s">
-        <v>1480</v>
+        <v>1405</v>
       </c>
       <c r="CB17">
         <v>47492639431.699997</v>
@@ -7814,46 +7816,46 @@
         <v>236.20438263634099</v>
       </c>
       <c r="E18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>1229</v>
+        <v>1216</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>1322</v>
+        <v>1309</v>
       </c>
       <c r="S18">
         <v>17.04</v>
@@ -7862,10 +7864,10 @@
         <v>305.95</v>
       </c>
       <c r="U18" s="7" t="s">
-        <v>1365</v>
+        <v>1347</v>
       </c>
       <c r="CA18" t="s">
-        <v>1481</v>
+        <v>1406</v>
       </c>
       <c r="CB18">
         <v>47605290416.489998</v>
@@ -7886,46 +7888,46 @@
         <v>239.126720417028</v>
       </c>
       <c r="E19" t="s">
+        <v>210</v>
+      </c>
+      <c r="F19" t="s">
         <v>211</v>
       </c>
-      <c r="F19" t="s">
-        <v>212</v>
-      </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>1228</v>
+        <v>1215</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>1331</v>
+        <v>1318</v>
       </c>
       <c r="S19">
         <v>16.78</v>
@@ -7934,7 +7936,7 @@
         <v>305.75</v>
       </c>
       <c r="U19" s="7" t="s">
-        <v>1366</v>
+        <v>1348</v>
       </c>
       <c r="V19">
         <v>5764.58</v>
@@ -8108,7 +8110,7 @@
         <v>30955.3</v>
       </c>
       <c r="CA19" t="s">
-        <v>1546</v>
+        <v>1471</v>
       </c>
       <c r="CB19">
         <v>47788529071.25</v>
@@ -8129,46 +8131,46 @@
         <v>241.83402955285499</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>1227</v>
+        <v>1214</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>1322</v>
+        <v>1309</v>
       </c>
       <c r="S20">
         <v>16.834782417833001</v>
@@ -8177,10 +8179,10 @@
         <v>305.89999999999998</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>1367</v>
+        <v>1349</v>
       </c>
       <c r="CA20" t="s">
-        <v>1482</v>
+        <v>1407</v>
       </c>
       <c r="CB20">
         <v>47119702152.489998</v>
@@ -8201,46 +8203,46 @@
         <v>244.368625500989</v>
       </c>
       <c r="E21" t="s">
+        <v>206</v>
+      </c>
+      <c r="F21" t="s">
         <v>207</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>208</v>
       </c>
-      <c r="G21" t="s">
-        <v>209</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>1226</v>
+        <v>1213</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>1330</v>
+        <v>1317</v>
       </c>
       <c r="S21">
         <v>16.650612381851399</v>
@@ -8249,10 +8251,10 @@
         <v>306.14999999999998</v>
       </c>
       <c r="U21" s="7" t="s">
-        <v>1368</v>
+        <v>1350</v>
       </c>
       <c r="CA21" t="s">
-        <v>1483</v>
+        <v>1408</v>
       </c>
       <c r="CB21">
         <v>45838593558.720001</v>
@@ -8273,46 +8275,46 @@
         <v>246.41222077366601</v>
       </c>
       <c r="E22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>1225</v>
+        <v>1212</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>1329</v>
+        <v>1316</v>
       </c>
       <c r="S22">
         <v>16.588186804893901</v>
@@ -8321,7 +8323,7 @@
         <v>306.35000000000002</v>
       </c>
       <c r="U22" s="7" t="s">
-        <v>1369</v>
+        <v>1351</v>
       </c>
       <c r="V22">
         <v>8516.6299999999992</v>
@@ -8495,7 +8497,7 @@
         <v>33781.03</v>
       </c>
       <c r="CA22" t="s">
-        <v>1547</v>
+        <v>1472</v>
       </c>
       <c r="CB22">
         <v>44305099103.879997</v>
@@ -8516,46 +8518,46 @@
         <v>248.23396876626299</v>
       </c>
       <c r="E23" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" t="s">
         <v>203</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>204</v>
       </c>
-      <c r="G23" t="s">
-        <v>205</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>1224</v>
+        <v>1211</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>1328</v>
+        <v>1315</v>
       </c>
       <c r="S23">
         <v>16.526946691677299</v>
@@ -8564,10 +8566,10 @@
         <v>306.60000000000002</v>
       </c>
       <c r="U23" s="7" t="s">
-        <v>1370</v>
+        <v>1352</v>
       </c>
       <c r="CA23" t="s">
-        <v>1484</v>
+        <v>1409</v>
       </c>
       <c r="CB23">
         <v>41995242740.389999</v>
@@ -8588,46 +8590,46 @@
         <v>250.222361823201</v>
       </c>
       <c r="E24" t="s">
+        <v>200</v>
+      </c>
+      <c r="F24" t="s">
         <v>201</v>
       </c>
-      <c r="F24" t="s">
-        <v>202</v>
-      </c>
       <c r="G24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>1223</v>
+        <v>1210</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>1325</v>
+        <v>1312</v>
       </c>
       <c r="S24">
         <v>16.635526973024401</v>
@@ -8636,10 +8638,10 @@
         <v>306.8</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="CA24" t="s">
-        <v>1485</v>
+        <v>1410</v>
       </c>
       <c r="CB24">
         <v>42167181452.089996</v>
@@ -8660,46 +8662,46 @@
         <v>252.07125822737501</v>
       </c>
       <c r="E25" t="s">
+        <v>198</v>
+      </c>
+      <c r="F25" t="s">
         <v>199</v>
       </c>
-      <c r="F25" t="s">
-        <v>200</v>
-      </c>
       <c r="G25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>1222</v>
+        <v>1209</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>1327</v>
+        <v>1314</v>
       </c>
       <c r="S25">
         <v>16.170708306982799</v>
@@ -8708,7 +8710,7 @@
         <v>307</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>1372</v>
+        <v>1354</v>
       </c>
       <c r="V25">
         <v>8132.22</v>
@@ -8882,7 +8884,7 @@
         <v>35667.629999999997</v>
       </c>
       <c r="CA25" t="s">
-        <v>1486</v>
+        <v>1411</v>
       </c>
       <c r="CB25">
         <v>43116863592.93</v>
@@ -8905,46 +8907,46 @@
         <v>253.93116089749299</v>
       </c>
       <c r="E26" t="s">
+        <v>195</v>
+      </c>
+      <c r="F26" t="s">
         <v>196</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>197</v>
       </c>
-      <c r="G26" t="s">
-        <v>198</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>1221</v>
+        <v>1208</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>1326</v>
+        <v>1313</v>
       </c>
       <c r="S26">
         <v>16.012933740000001</v>
@@ -8953,10 +8955,10 @@
         <v>306.75</v>
       </c>
       <c r="U26" s="7" t="s">
-        <v>1373</v>
+        <v>1355</v>
       </c>
       <c r="CA26" t="s">
-        <v>1487</v>
+        <v>1412</v>
       </c>
       <c r="CB26">
         <v>43174283435.470001</v>
@@ -8977,46 +8979,46 @@
         <v>255.78511048991601</v>
       </c>
       <c r="E27" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" t="s">
         <v>194</v>
       </c>
-      <c r="F27" t="s">
-        <v>195</v>
-      </c>
       <c r="G27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>1220</v>
+        <v>1207</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>1325</v>
+        <v>1312</v>
       </c>
       <c r="S27">
         <v>16.077860319999999</v>
@@ -9025,10 +9027,10 @@
         <v>306.85000000000002</v>
       </c>
       <c r="U27" s="7" t="s">
-        <v>1374</v>
+        <v>1356</v>
       </c>
       <c r="CA27" t="s">
-        <v>1488</v>
+        <v>1413</v>
       </c>
       <c r="CB27">
         <v>42296734110.709999</v>
@@ -9049,46 +9051,46 @@
         <v>257.797113894429</v>
       </c>
       <c r="E28" t="s">
+        <v>190</v>
+      </c>
+      <c r="F28" t="s">
         <v>191</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>192</v>
       </c>
-      <c r="G28" t="s">
-        <v>193</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>1106</v>
+        <v>1094</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>1219</v>
+        <v>1206</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>1324</v>
+        <v>1311</v>
       </c>
       <c r="S28">
         <v>14.92485233</v>
@@ -9097,7 +9099,7 @@
         <v>306.95</v>
       </c>
       <c r="U28" s="7" t="s">
-        <v>1375</v>
+        <v>1357</v>
       </c>
       <c r="V28">
         <v>6077.2</v>
@@ -9271,7 +9273,7 @@
         <v>32086.12</v>
       </c>
       <c r="CA28" t="s">
-        <v>1548</v>
+        <v>1473</v>
       </c>
       <c r="CB28">
         <v>44428102947.32</v>
@@ -9292,46 +9294,46 @@
         <v>260.23108429292103</v>
       </c>
       <c r="E29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F29" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>1218</v>
+        <v>1205</v>
       </c>
       <c r="Q29" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="R29" s="2" t="s">
         <v>1310</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>1323</v>
       </c>
       <c r="S29">
         <v>15.39433275</v>
@@ -9340,10 +9342,10 @@
         <v>306.95</v>
       </c>
       <c r="U29" s="7" t="s">
-        <v>1376</v>
+        <v>1358</v>
       </c>
       <c r="CA29" t="s">
-        <v>1489</v>
+        <v>1414</v>
       </c>
       <c r="CB29">
         <v>44792699904.760002</v>
@@ -9364,46 +9366,46 @@
         <v>263.12319017277298</v>
       </c>
       <c r="E30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>1217</v>
+        <v>1204</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>1322</v>
+        <v>1309</v>
       </c>
       <c r="S30">
         <v>15.32671491</v>
@@ -9412,10 +9414,10 @@
         <v>306.95</v>
       </c>
       <c r="U30" s="7" t="s">
-        <v>1377</v>
+        <v>1359</v>
       </c>
       <c r="CA30" t="s">
-        <v>1490</v>
+        <v>1415</v>
       </c>
       <c r="CB30">
         <v>45122817866.019997</v>
@@ -9436,46 +9438,46 @@
         <v>265.95032003764499</v>
       </c>
       <c r="E31" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F31" t="s">
+        <v>182</v>
+      </c>
+      <c r="G31" t="s">
         <v>183</v>
       </c>
-      <c r="G31" t="s">
-        <v>184</v>
-      </c>
       <c r="H31" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>1216</v>
+        <v>1203</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>1321</v>
+        <v>1308</v>
       </c>
       <c r="S31">
         <v>15.795169059999999</v>
@@ -9484,7 +9486,7 @@
         <v>306.89999999999998</v>
       </c>
       <c r="U31" s="7" t="s">
-        <v>1378</v>
+        <v>1360</v>
       </c>
       <c r="V31">
         <v>6788.6</v>
@@ -9658,7 +9660,7 @@
         <v>35300.949999999997</v>
       </c>
       <c r="CA31" t="s">
-        <v>1549</v>
+        <v>1474</v>
       </c>
       <c r="CB31">
         <v>45069454867.589996</v>
@@ -9679,46 +9681,46 @@
         <v>268.64001862793702</v>
       </c>
       <c r="E32" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32" t="s">
         <v>185</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>186</v>
       </c>
-      <c r="G32" t="s">
-        <v>187</v>
-      </c>
       <c r="H32" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>1215</v>
+        <v>1202</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>1320</v>
+        <v>1307</v>
       </c>
       <c r="S32">
         <v>15.4628034</v>
@@ -9727,10 +9729,10 @@
         <v>306.85000000000002</v>
       </c>
       <c r="U32" s="7" t="s">
-        <v>1377</v>
+        <v>1359</v>
       </c>
       <c r="CA32" t="s">
-        <v>1491</v>
+        <v>1416</v>
       </c>
       <c r="CB32">
         <v>44903031403.580002</v>
@@ -9751,46 +9753,46 @@
         <v>271.28805191634098</v>
       </c>
       <c r="E33" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" t="s">
         <v>182</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>183</v>
       </c>
-      <c r="G33" t="s">
-        <v>184</v>
-      </c>
       <c r="H33" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>1101</v>
+        <v>1089</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>1214</v>
+        <v>1201</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>1319</v>
+        <v>1306</v>
       </c>
       <c r="S33">
         <v>15.40057483</v>
@@ -9799,10 +9801,10 @@
         <v>307</v>
       </c>
       <c r="U33" s="7" t="s">
-        <v>1379</v>
+        <v>1361</v>
       </c>
       <c r="CA33" t="s">
-        <v>1550</v>
+        <v>1475</v>
       </c>
       <c r="CB33">
         <v>43607804397.709999</v>
@@ -9823,46 +9825,46 @@
         <v>274.11820661883797</v>
       </c>
       <c r="E34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F34" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" t="s">
         <v>171</v>
       </c>
-      <c r="G34" t="s">
-        <v>172</v>
-      </c>
       <c r="H34" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>1213</v>
+        <v>1200</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>1318</v>
+        <v>1305</v>
       </c>
       <c r="S34">
         <v>15.1529851</v>
@@ -9871,7 +9873,7 @@
         <v>307</v>
       </c>
       <c r="U34" s="7" t="s">
-        <v>1380</v>
+        <v>1362</v>
       </c>
       <c r="V34">
         <v>9783.5400000000009</v>
@@ -10045,7 +10047,7 @@
         <v>38222.339999999997</v>
       </c>
       <c r="CA34" t="s">
-        <v>1492</v>
+        <v>1417</v>
       </c>
       <c r="CB34">
         <v>41852286712.260002</v>
@@ -10066,46 +10068,46 @@
         <v>277.04643935864499</v>
       </c>
       <c r="E35" t="s">
+        <v>177</v>
+      </c>
+      <c r="F35" t="s">
         <v>178</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>179</v>
       </c>
-      <c r="G35" t="s">
-        <v>180</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>1099</v>
+        <v>1087</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>1212</v>
+        <v>1199</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>1317</v>
+        <v>1304</v>
       </c>
       <c r="S35">
         <v>15.073976999999999</v>
@@ -10114,10 +10116,10 @@
         <v>307</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>1379</v>
+        <v>1361</v>
       </c>
       <c r="CA35" t="s">
-        <v>1493</v>
+        <v>1418</v>
       </c>
       <c r="CB35">
         <v>40464165373.190002</v>
@@ -10138,46 +10140,46 @@
         <v>279.88251392826197</v>
       </c>
       <c r="E36" t="s">
+        <v>175</v>
+      </c>
+      <c r="F36" t="s">
         <v>176</v>
       </c>
-      <c r="F36" t="s">
-        <v>177</v>
-      </c>
       <c r="G36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>1098</v>
+        <v>1086</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>1211</v>
+        <v>1198</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>1316</v>
+        <v>1303</v>
       </c>
       <c r="S36">
         <v>14.911702010000001</v>
@@ -10186,10 +10188,10 @@
         <v>307</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>1381</v>
+        <v>1363</v>
       </c>
       <c r="CA36" t="s">
-        <v>1551</v>
+        <v>1476</v>
       </c>
       <c r="CB36">
         <v>39803153018.889999</v>
@@ -10210,46 +10212,46 @@
         <v>282.27335068299499</v>
       </c>
       <c r="E37" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" t="s">
         <v>174</v>
       </c>
-      <c r="F37" t="s">
-        <v>175</v>
-      </c>
       <c r="G37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>1210</v>
+        <v>1197</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>1315</v>
+        <v>1302</v>
       </c>
       <c r="S37">
         <v>14.985138320000001</v>
@@ -10258,7 +10260,7 @@
         <v>307</v>
       </c>
       <c r="U37" s="7" t="s">
-        <v>1382</v>
+        <v>1364</v>
       </c>
       <c r="V37">
         <v>9254.7900000000009</v>
@@ -10432,7 +10434,7 @@
         <v>40029.72</v>
       </c>
       <c r="CA37" t="s">
-        <v>1494</v>
+        <v>1419</v>
       </c>
       <c r="CB37">
         <v>38595257595.93</v>
@@ -10455,46 +10457,46 @@
         <v>284.738865786524</v>
       </c>
       <c r="E38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F38" t="s">
+        <v>170</v>
+      </c>
+      <c r="G38" t="s">
         <v>171</v>
       </c>
-      <c r="G38" t="s">
-        <v>172</v>
-      </c>
       <c r="H38" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>1209</v>
+        <v>1196</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>1314</v>
+        <v>1301</v>
       </c>
       <c r="S38">
         <v>14.97193036</v>
@@ -10503,10 +10505,10 @@
         <v>307</v>
       </c>
       <c r="U38" s="7" t="s">
-        <v>1383</v>
+        <v>1365</v>
       </c>
       <c r="CA38" t="s">
-        <v>1495</v>
+        <v>1420</v>
       </c>
       <c r="CB38">
         <v>38009763479.699997</v>
@@ -10527,46 +10529,46 @@
         <v>286.98714284023202</v>
       </c>
       <c r="E39" t="s">
+        <v>169</v>
+      </c>
+      <c r="F39" t="s">
         <v>170</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>171</v>
       </c>
-      <c r="G39" t="s">
-        <v>172</v>
-      </c>
       <c r="H39" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>1095</v>
+        <v>1083</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>1208</v>
+        <v>1195</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>1313</v>
+        <v>1300</v>
       </c>
       <c r="S39">
         <v>15.043394299999999</v>
@@ -10575,10 +10577,10 @@
         <v>306.95</v>
       </c>
       <c r="U39" s="7" t="s">
-        <v>1384</v>
+        <v>1366</v>
       </c>
       <c r="CA39" t="s">
-        <v>1552</v>
+        <v>1477</v>
       </c>
       <c r="CB39">
         <v>36299517218.459999</v>
@@ -10599,46 +10601,46 @@
         <v>289.39614348106102</v>
       </c>
       <c r="E40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F40" t="s">
+        <v>166</v>
+      </c>
+      <c r="G40" t="s">
         <v>167</v>
       </c>
-      <c r="G40" t="s">
-        <v>168</v>
-      </c>
       <c r="H40" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>1207</v>
+        <v>1194</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>1312</v>
+        <v>1299</v>
       </c>
       <c r="S40">
         <v>14.70798549</v>
@@ -10647,7 +10649,7 @@
         <v>361</v>
       </c>
       <c r="U40" s="7" t="s">
-        <v>1385</v>
+        <v>1367</v>
       </c>
       <c r="V40">
         <v>7442.68</v>
@@ -10821,7 +10823,7 @@
         <v>35969.9</v>
       </c>
       <c r="CA40" t="s">
-        <v>1496</v>
+        <v>1421</v>
       </c>
       <c r="CB40">
         <v>35164442405.720001</v>
@@ -10842,46 +10844,46 @@
         <v>292.34741228792802</v>
       </c>
       <c r="E41" t="s">
+        <v>165</v>
+      </c>
+      <c r="F41" t="s">
         <v>166</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>167</v>
       </c>
-      <c r="G41" t="s">
-        <v>168</v>
-      </c>
       <c r="H41" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>1206</v>
+        <v>1193</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>1311</v>
+        <v>1298</v>
       </c>
       <c r="S41">
         <v>14.9191304501911</v>
@@ -10890,10 +10892,10 @@
         <v>361</v>
       </c>
       <c r="U41" s="7" t="s">
-        <v>1386</v>
+        <v>1368</v>
       </c>
       <c r="CA41" t="s">
-        <v>1497</v>
+        <v>1422</v>
       </c>
       <c r="CB41">
         <v>33520904270.720001</v>
@@ -10914,46 +10916,46 @@
         <v>295.76164529559401</v>
       </c>
       <c r="E42" t="s">
+        <v>162</v>
+      </c>
+      <c r="F42" t="s">
         <v>163</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>164</v>
       </c>
-      <c r="G42" t="s">
-        <v>165</v>
-      </c>
       <c r="H42" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>1205</v>
+        <v>1192</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>1308</v>
+        <v>1295</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>1300</v>
+        <v>1287</v>
       </c>
       <c r="S42">
         <v>14.731420147388301</v>
@@ -10962,10 +10964,10 @@
         <v>361</v>
       </c>
       <c r="U42" s="7" t="s">
-        <v>1387</v>
+        <v>1369</v>
       </c>
       <c r="CA42" t="s">
-        <v>1553</v>
+        <v>1478</v>
       </c>
       <c r="CB42">
         <v>36594997046.980003</v>
@@ -10986,46 +10988,46 @@
         <v>299.35027524677201</v>
       </c>
       <c r="E43" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" t="s">
         <v>161</v>
       </c>
-      <c r="F43" t="s">
-        <v>162</v>
-      </c>
       <c r="G43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>1204</v>
+        <v>1191</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>1308</v>
+        <v>1295</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S43">
         <v>15.6538447898819</v>
@@ -11034,7 +11036,7 @@
         <v>361</v>
       </c>
       <c r="U43" s="7" t="s">
-        <v>1388</v>
+        <v>1370</v>
       </c>
       <c r="V43">
         <v>8139.52</v>
@@ -11208,7 +11210,7 @@
         <v>34336.9</v>
       </c>
       <c r="CA43" t="s">
-        <v>1498</v>
+        <v>1423</v>
       </c>
       <c r="CB43">
         <v>36185274656.099998</v>
@@ -11229,46 +11231,46 @@
         <v>303.081596543194</v>
       </c>
       <c r="E44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F44" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>1090</v>
+        <v>1078</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>1203</v>
+        <v>1190</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>1308</v>
+        <v>1295</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S44">
         <v>14.993308614541901</v>
@@ -11277,10 +11279,10 @@
         <v>381</v>
       </c>
       <c r="U44" s="7" t="s">
-        <v>1389</v>
+        <v>1371</v>
       </c>
       <c r="CA44" t="s">
-        <v>1554</v>
+        <v>1479</v>
       </c>
       <c r="CB44">
         <v>35877636049.949997</v>
@@ -11301,46 +11303,46 @@
         <v>307.15101262994102</v>
       </c>
       <c r="E45" t="s">
+        <v>157</v>
+      </c>
+      <c r="F45" t="s">
         <v>158</v>
       </c>
-      <c r="F45" t="s">
-        <v>159</v>
-      </c>
       <c r="G45" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>1089</v>
+        <v>1077</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>1202</v>
+        <v>1189</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>1308</v>
+        <v>1295</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>1309</v>
+        <v>1296</v>
       </c>
       <c r="S45">
         <v>11.791415754612</v>
@@ -11349,10 +11351,10 @@
         <v>381</v>
       </c>
       <c r="U45" s="7" t="s">
-        <v>1390</v>
+        <v>1372</v>
       </c>
       <c r="CA45" t="s">
-        <v>1499</v>
+        <v>1424</v>
       </c>
       <c r="CB45">
         <v>35671263210.879997</v>
@@ -11373,46 +11375,46 @@
         <v>311.69057280195602</v>
       </c>
       <c r="E46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F46" t="s">
+        <v>55</v>
+      </c>
+      <c r="G46" t="s">
         <v>56</v>
       </c>
-      <c r="G46" t="s">
-        <v>57</v>
-      </c>
       <c r="H46" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>1201</v>
+        <v>1188</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>1307</v>
+        <v>1294</v>
       </c>
       <c r="S46">
         <v>11.551408937643901</v>
@@ -11421,7 +11423,7 @@
         <v>381</v>
       </c>
       <c r="U46" s="7" t="s">
-        <v>1391</v>
+        <v>1373</v>
       </c>
       <c r="V46">
         <v>11105.99</v>
@@ -11595,7 +11597,7 @@
         <v>39714.720000000001</v>
       </c>
       <c r="CA46" t="s">
-        <v>1500</v>
+        <v>1425</v>
       </c>
       <c r="CB46">
         <v>35738842863.709999</v>
@@ -11616,46 +11618,46 @@
         <v>316.47774635164598</v>
       </c>
       <c r="E47" t="s">
+        <v>154</v>
+      </c>
+      <c r="F47" t="s">
         <v>155</v>
       </c>
-      <c r="F47" t="s">
-        <v>156</v>
-      </c>
       <c r="G47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>1200</v>
+        <v>1187</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S47">
         <v>11.3088406889607</v>
@@ -11664,10 +11666,10 @@
         <v>381</v>
       </c>
       <c r="U47" s="7" t="s">
-        <v>1392</v>
+        <v>1374</v>
       </c>
       <c r="CA47" t="s">
-        <v>1555</v>
+        <v>1480</v>
       </c>
       <c r="CB47">
         <v>35689545008.080002</v>
@@ -11688,46 +11690,46 @@
         <v>321.54935333609802</v>
       </c>
       <c r="E48" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F48" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" t="s">
         <v>56</v>
       </c>
-      <c r="G48" t="s">
-        <v>57</v>
-      </c>
       <c r="H48" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>1199</v>
+        <v>1186</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>1306</v>
+        <v>1293</v>
       </c>
       <c r="S48">
         <v>12.680480037177601</v>
@@ -11736,10 +11738,10 @@
         <v>381</v>
       </c>
       <c r="U48" s="7" t="s">
-        <v>1393</v>
+        <v>1375</v>
       </c>
       <c r="CA48" t="s">
-        <v>1556</v>
+        <v>1481</v>
       </c>
       <c r="CB48">
         <v>35413202793.050003</v>
@@ -11760,46 +11762,46 @@
         <v>326.74096301994501</v>
       </c>
       <c r="E49" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G49" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>1306</v>
+        <v>1293</v>
       </c>
       <c r="S49">
         <v>11.351100492157499</v>
@@ -11808,7 +11810,7 @@
         <v>381</v>
       </c>
       <c r="U49" s="7" t="s">
-        <v>1394</v>
+        <v>1376</v>
       </c>
       <c r="V49">
         <v>10553.42</v>
@@ -11982,7 +11984,7 @@
         <v>44230.8</v>
       </c>
       <c r="CA49" t="s">
-        <v>1501</v>
+        <v>1426</v>
       </c>
       <c r="CB49">
         <v>35373915212.720001</v>
@@ -12005,46 +12007,46 @@
         <v>331.62495627901097</v>
       </c>
       <c r="E50" t="s">
+        <v>149</v>
+      </c>
+      <c r="F50" t="s">
         <v>150</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>151</v>
       </c>
-      <c r="G50" t="s">
-        <v>152</v>
-      </c>
       <c r="H50" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>1084</v>
+        <v>1072</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>1197</v>
+        <v>1184</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S50">
         <v>11.2451661330151</v>
@@ -12053,10 +12055,10 @@
         <v>381</v>
       </c>
       <c r="U50" s="7" t="s">
-        <v>1395</v>
+        <v>1377</v>
       </c>
       <c r="CA50" t="s">
-        <v>1557</v>
+        <v>1482</v>
       </c>
       <c r="CB50">
         <v>36303090978.120003</v>
@@ -12077,46 +12079,46 @@
         <v>336.73606648503699</v>
       </c>
       <c r="E51" t="s">
+        <v>147</v>
+      </c>
+      <c r="F51" t="s">
         <v>148</v>
       </c>
-      <c r="F51" t="s">
-        <v>149</v>
-      </c>
       <c r="G51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>1083</v>
+        <v>1071</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>1196</v>
+        <v>1183</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S51">
         <v>11.208910989846901</v>
@@ -12125,10 +12127,10 @@
         <v>381</v>
       </c>
       <c r="U51" s="7" t="s">
-        <v>1396</v>
+        <v>1378</v>
       </c>
       <c r="CA51" t="s">
-        <v>1558</v>
+        <v>1483</v>
       </c>
       <c r="CB51">
         <v>35099861581.910004</v>
@@ -12149,46 +12151,46 @@
         <v>341.98338093990702</v>
       </c>
       <c r="E52" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F52" t="s">
+        <v>40</v>
+      </c>
+      <c r="G52" t="s">
         <v>41</v>
       </c>
-      <c r="G52" t="s">
-        <v>42</v>
-      </c>
       <c r="H52" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>1082</v>
+        <v>1070</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>1195</v>
+        <v>1182</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S52">
         <v>11.134877193248</v>
@@ -12197,7 +12199,7 @@
         <v>381</v>
       </c>
       <c r="U52" s="7" t="s">
-        <v>1397</v>
+        <v>1379</v>
       </c>
       <c r="V52">
         <v>8569.33</v>
@@ -12371,7 +12373,7 @@
         <v>40507.69</v>
       </c>
       <c r="CA52" t="s">
-        <v>1502</v>
+        <v>1427</v>
       </c>
       <c r="CB52">
         <v>34820456887.349998</v>
@@ -12392,46 +12394,46 @@
         <v>345.31121928266998</v>
       </c>
       <c r="E53" t="s">
+        <v>143</v>
+      </c>
+      <c r="F53" t="s">
         <v>144</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>145</v>
       </c>
-      <c r="G53" t="s">
-        <v>146</v>
-      </c>
       <c r="H53" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>1081</v>
+        <v>1069</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>1194</v>
+        <v>1181</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S53">
         <v>11.2387475338329</v>
@@ -12440,10 +12442,10 @@
         <v>381</v>
       </c>
       <c r="U53" s="7" t="s">
-        <v>1398</v>
+        <v>1380</v>
       </c>
       <c r="CA53" t="s">
-        <v>1503</v>
+        <v>1428</v>
       </c>
       <c r="CB53">
         <v>34881389455.489998</v>
@@ -12464,46 +12466,46 @@
         <v>348.80082348823697</v>
       </c>
       <c r="E54" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F54" t="s">
+        <v>84</v>
+      </c>
+      <c r="G54" t="s">
         <v>85</v>
       </c>
-      <c r="G54" t="s">
-        <v>86</v>
-      </c>
       <c r="H54" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>1080</v>
+        <v>1068</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>1193</v>
+        <v>1180</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
       <c r="S54">
         <v>11.286631215263601</v>
@@ -12512,10 +12514,10 @@
         <v>410.75</v>
       </c>
       <c r="U54" s="7" t="s">
-        <v>1399</v>
+        <v>1381</v>
       </c>
       <c r="CA54" t="s">
-        <v>1504</v>
+        <v>1429</v>
       </c>
       <c r="CB54">
         <v>34229048746.130001</v>
@@ -12536,46 +12538,46 @@
         <v>352.48721596865801</v>
       </c>
       <c r="E55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F55" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" t="s">
         <v>26</v>
       </c>
-      <c r="G55" t="s">
-        <v>27</v>
-      </c>
       <c r="H55" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>1079</v>
+        <v>1067</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>1192</v>
+        <v>1179</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
       <c r="S55">
         <v>11.6700892888315</v>
@@ -12584,7 +12586,7 @@
         <v>410.12</v>
       </c>
       <c r="U55" s="7" t="s">
-        <v>1400</v>
+        <v>1382</v>
       </c>
       <c r="V55">
         <v>8657.31</v>
@@ -12758,7 +12760,7 @@
         <v>39614.839999999997</v>
       </c>
       <c r="CA55" t="s">
-        <v>1505</v>
+        <v>1430</v>
       </c>
       <c r="CB55">
         <v>33323503869.259998</v>
@@ -12779,46 +12781,46 @@
         <v>355.74838970375401</v>
       </c>
       <c r="E56" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F56" t="s">
+        <v>65</v>
+      </c>
+      <c r="G56" t="s">
         <v>66</v>
       </c>
-      <c r="G56" t="s">
-        <v>67</v>
-      </c>
       <c r="H56" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>1191</v>
+        <v>1178</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
       <c r="S56">
         <v>11.572884821223001</v>
@@ -12827,10 +12829,10 @@
         <v>410.12</v>
       </c>
       <c r="U56" s="7" t="s">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="CA56" t="s">
-        <v>1559</v>
+        <v>1484</v>
       </c>
       <c r="CB56">
         <v>33402616891.939999</v>
@@ -12851,46 +12853,46 @@
         <v>359.39471713218802</v>
       </c>
       <c r="E57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F57" t="s">
+        <v>110</v>
+      </c>
+      <c r="G57" t="s">
         <v>111</v>
       </c>
-      <c r="G57" t="s">
-        <v>112</v>
-      </c>
       <c r="H57" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>1077</v>
+        <v>1065</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>1190</v>
+        <v>1177</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
       <c r="S57">
         <v>11.620572942616</v>
@@ -12899,10 +12901,10 @@
         <v>410.39</v>
       </c>
       <c r="U57" s="7" t="s">
-        <v>1402</v>
+        <v>1384</v>
       </c>
       <c r="CA57" t="s">
-        <v>1506</v>
+        <v>1431</v>
       </c>
       <c r="CB57">
         <v>34017914833.450001</v>
@@ -12923,46 +12925,46 @@
         <v>363.52430111236902</v>
       </c>
       <c r="E58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F58" t="s">
+        <v>75</v>
+      </c>
+      <c r="G58" t="s">
         <v>76</v>
       </c>
-      <c r="G58" t="s">
-        <v>77</v>
-      </c>
       <c r="H58" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>1076</v>
+        <v>1064</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>1189</v>
+        <v>1176</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
       <c r="S58">
         <v>11.7329850215693</v>
@@ -12971,7 +12973,7 @@
         <v>410.8</v>
       </c>
       <c r="U58" s="7" t="s">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="V58">
         <v>11988.58</v>
@@ -13145,7 +13147,7 @@
         <v>45850.28</v>
       </c>
       <c r="CA58" t="s">
-        <v>1507</v>
+        <v>1432</v>
       </c>
       <c r="CB58">
         <v>36782343499.620003</v>
@@ -13166,46 +13168,46 @@
         <v>367.09386733673603</v>
       </c>
       <c r="E59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F59" t="s">
+        <v>79</v>
+      </c>
+      <c r="G59" t="s">
         <v>80</v>
       </c>
-      <c r="G59" t="s">
-        <v>81</v>
-      </c>
       <c r="H59" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>1188</v>
+        <v>1175</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
       <c r="S59">
         <v>11.6097329628683</v>
@@ -13214,10 +13216,10 @@
         <v>411.25</v>
       </c>
       <c r="U59" s="7" t="s">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="CA59" t="s">
-        <v>1560</v>
+        <v>1485</v>
       </c>
       <c r="CB59">
         <v>41828981480.480003</v>
@@ -13238,46 +13240,46 @@
         <v>371.05413355784998</v>
       </c>
       <c r="E60" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F60" t="s">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s">
         <v>80</v>
       </c>
-      <c r="G60" t="s">
-        <v>81</v>
-      </c>
       <c r="H60" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>1074</v>
+        <v>1062</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>1187</v>
+        <v>1174</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
       <c r="S60">
         <v>11.7964167817162</v>
@@ -13286,10 +13288,10 @@
         <v>410</v>
       </c>
       <c r="U60" s="7" t="s">
-        <v>1405</v>
+        <v>1387</v>
       </c>
       <c r="CA60" t="s">
-        <v>1508</v>
+        <v>1433</v>
       </c>
       <c r="CB60">
         <v>41186700542.290001</v>
@@ -13310,46 +13312,46 @@
         <v>377.79583576688799</v>
       </c>
       <c r="E61" t="s">
+        <v>133</v>
+      </c>
+      <c r="F61" t="s">
         <v>134</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>135</v>
       </c>
-      <c r="G61" t="s">
-        <v>136</v>
-      </c>
       <c r="H61" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>1073</v>
+        <v>1061</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>1186</v>
+        <v>1173</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>1304</v>
+        <v>1291</v>
       </c>
       <c r="S61">
         <v>11.6805786525335</v>
@@ -13358,7 +13360,7 @@
         <v>435</v>
       </c>
       <c r="U61" s="7" t="s">
-        <v>1406</v>
+        <v>1388</v>
       </c>
       <c r="V61">
         <v>11910.84</v>
@@ -13532,7 +13534,7 @@
         <v>50102.7</v>
       </c>
       <c r="CA61" t="s">
-        <v>1509</v>
+        <v>1434</v>
       </c>
       <c r="CB61">
         <v>40520531729.93</v>
@@ -13555,46 +13557,46 @@
         <v>383.36025528724701</v>
       </c>
       <c r="E62" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F62" t="s">
+        <v>34</v>
+      </c>
+      <c r="G62" t="s">
         <v>35</v>
       </c>
-      <c r="G62" t="s">
-        <v>36</v>
-      </c>
       <c r="H62" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>1072</v>
+        <v>1060</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>1185</v>
+        <v>1172</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>1304</v>
+        <v>1291</v>
       </c>
       <c r="S62">
         <v>11.6756479720841</v>
@@ -13603,10 +13605,10 @@
         <v>412</v>
       </c>
       <c r="U62" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="CA62" t="s">
-        <v>1510</v>
+        <v>1435</v>
       </c>
       <c r="CB62">
         <v>40039162875.910004</v>
@@ -13627,46 +13629,46 @@
         <v>389.61186465230497</v>
       </c>
       <c r="E63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F63" t="s">
+        <v>95</v>
+      </c>
+      <c r="G63" t="s">
         <v>96</v>
       </c>
-      <c r="G63" t="s">
-        <v>97</v>
-      </c>
       <c r="H63" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>1071</v>
+        <v>1059</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>1184</v>
+        <v>1171</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>1303</v>
+        <v>1290</v>
       </c>
       <c r="S63">
         <v>11.782088338965901</v>
@@ -13675,10 +13677,10 @@
         <v>417</v>
       </c>
       <c r="U63" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="CA63" t="s">
-        <v>1511</v>
+        <v>1436</v>
       </c>
       <c r="CB63">
         <v>39863413918.07</v>
@@ -13699,46 +13701,46 @@
         <v>396.41055986396799</v>
       </c>
       <c r="E64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F64" t="s">
+        <v>110</v>
+      </c>
+      <c r="G64" t="s">
         <v>111</v>
       </c>
-      <c r="G64" t="s">
-        <v>112</v>
-      </c>
       <c r="H64" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>1070</v>
+        <v>1058</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>1183</v>
+        <v>1170</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S64">
         <v>11.8359019561676</v>
@@ -13747,7 +13749,7 @@
         <v>416</v>
       </c>
       <c r="U64" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="V64">
         <v>9558.99</v>
@@ -13921,7 +13923,7 @@
         <v>45902.64</v>
       </c>
       <c r="CA64" t="s">
-        <v>1512</v>
+        <v>1437</v>
       </c>
       <c r="CB64">
         <v>39546756727.809998</v>
@@ -13942,46 +13944,46 @@
         <v>403.388465236586</v>
       </c>
       <c r="E65" t="s">
+        <v>127</v>
+      </c>
+      <c r="F65" t="s">
         <v>128</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>129</v>
       </c>
-      <c r="G65" t="s">
-        <v>130</v>
-      </c>
       <c r="H65" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>1069</v>
+        <v>1057</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>1182</v>
+        <v>1169</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>1302</v>
+        <v>1289</v>
       </c>
       <c r="S65">
         <v>11.828405941751599</v>
@@ -13990,10 +13992,10 @@
         <v>415</v>
       </c>
       <c r="U65" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="CA65" t="s">
-        <v>1561</v>
+        <v>1486</v>
       </c>
       <c r="CB65">
         <v>39579280535.540001</v>
@@ -14014,46 +14016,46 @@
         <v>410.57972535763099</v>
       </c>
       <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
+        <v>53</v>
+      </c>
+      <c r="G66" t="s">
         <v>126</v>
       </c>
-      <c r="F66" t="s">
-        <v>54</v>
-      </c>
-      <c r="G66" t="s">
-        <v>127</v>
-      </c>
       <c r="H66" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>1068</v>
+        <v>1056</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>1181</v>
+        <v>1168</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>1298</v>
+        <v>1285</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>1300</v>
+        <v>1287</v>
       </c>
       <c r="S66">
         <v>11.962937015066901</v>
@@ -14062,10 +14064,10 @@
         <v>417</v>
       </c>
       <c r="U66" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="CA66" t="s">
-        <v>1513</v>
+        <v>1438</v>
       </c>
       <c r="CB66">
         <v>38483657153.93</v>
@@ -14086,46 +14088,46 @@
         <v>418.03438438003701</v>
       </c>
       <c r="E67" t="s">
+        <v>122</v>
+      </c>
+      <c r="F67" t="s">
         <v>123</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>124</v>
       </c>
-      <c r="G67" t="s">
-        <v>125</v>
-      </c>
       <c r="H67" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>1180</v>
+        <v>1167</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>1298</v>
+        <v>1285</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>1299</v>
+        <v>1286</v>
       </c>
       <c r="S67">
         <v>12.2881297957447</v>
@@ -14134,7 +14136,7 @@
         <v>414</v>
       </c>
       <c r="U67" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="V67">
         <v>9854.73</v>
@@ -14308,7 +14310,7 @@
         <v>45505.29</v>
       </c>
       <c r="CA67" t="s">
-        <v>1514</v>
+        <v>1439</v>
       </c>
       <c r="CB67">
         <v>39155282548.199997</v>
@@ -14329,46 +14331,46 @@
         <v>425.62811777490799</v>
       </c>
       <c r="E68" t="s">
+        <v>120</v>
+      </c>
+      <c r="F68" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68" t="s">
         <v>121</v>
       </c>
-      <c r="F68" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" t="s">
-        <v>122</v>
-      </c>
       <c r="H68" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>1179</v>
+        <v>1166</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="S68">
         <v>12.1009991683471</v>
@@ -14377,10 +14379,10 @@
         <v>426</v>
       </c>
       <c r="U68" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="CA68" t="s">
-        <v>1562</v>
+        <v>1487</v>
       </c>
       <c r="CB68">
         <v>39219234945.940002</v>
@@ -14401,46 +14403,46 @@
         <v>433.15991492830398</v>
       </c>
       <c r="E69" t="s">
+        <v>117</v>
+      </c>
+      <c r="F69" t="s">
         <v>118</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>119</v>
       </c>
-      <c r="G69" t="s">
-        <v>120</v>
-      </c>
       <c r="H69" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>1178</v>
+        <v>1165</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>1296</v>
+        <v>1283</v>
       </c>
       <c r="S69">
         <v>12.2319507283382</v>
@@ -14449,10 +14451,10 @@
         <v>430</v>
       </c>
       <c r="U69" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="CA69" t="s">
-        <v>1515</v>
+        <v>1440</v>
       </c>
       <c r="CB69">
         <v>39024891148.440002</v>
@@ -14473,46 +14475,46 @@
         <v>439.041706007767</v>
       </c>
       <c r="E70" t="s">
+        <v>115</v>
+      </c>
+      <c r="F70" t="s">
+        <v>38</v>
+      </c>
+      <c r="G70" t="s">
         <v>116</v>
       </c>
-      <c r="F70" t="s">
-        <v>39</v>
-      </c>
-      <c r="G70" t="s">
-        <v>117</v>
-      </c>
       <c r="H70" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>1064</v>
+        <v>1052</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>1177</v>
+        <v>1164</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>1294</v>
+        <v>1281</v>
       </c>
       <c r="S70">
         <v>12.5436504133179</v>
@@ -14521,7 +14523,7 @@
         <v>435.1</v>
       </c>
       <c r="U70" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="V70">
         <v>14395.26</v>
@@ -14695,7 +14697,7 @@
         <v>53176.51</v>
       </c>
       <c r="CA70" t="s">
-        <v>1516</v>
+        <v>1441</v>
       </c>
       <c r="CB70">
         <v>38252906234.209999</v>
@@ -14716,46 +14718,46 @@
         <v>444.50337375644102</v>
       </c>
       <c r="E71" t="s">
+        <v>113</v>
+      </c>
+      <c r="F71" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71" t="s">
         <v>114</v>
       </c>
-      <c r="F71" t="s">
-        <v>30</v>
-      </c>
-      <c r="G71" t="s">
-        <v>115</v>
-      </c>
       <c r="H71" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>1176</v>
+        <v>1163</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>1293</v>
+        <v>1280</v>
       </c>
       <c r="S71">
         <v>12.7363467347834</v>
@@ -14764,10 +14766,10 @@
         <v>441</v>
       </c>
       <c r="U71" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="CA71" t="s">
-        <v>1517</v>
+        <v>1442</v>
       </c>
       <c r="CB71">
         <v>37386700903.440002</v>
@@ -14788,46 +14790,46 @@
         <v>450.703274239481</v>
       </c>
       <c r="E72" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F72" t="s">
+        <v>98</v>
+      </c>
+      <c r="G72" t="s">
         <v>99</v>
       </c>
-      <c r="G72" t="s">
-        <v>100</v>
-      </c>
       <c r="H72" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>1175</v>
+        <v>1162</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>1292</v>
+        <v>1279</v>
       </c>
       <c r="S72">
         <v>13.1742059941063</v>
@@ -14836,10 +14838,10 @@
         <v>446</v>
       </c>
       <c r="U72" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="CA72" t="s">
-        <v>1518</v>
+        <v>1443</v>
       </c>
       <c r="CB72">
         <v>37112947063</v>
@@ -14860,46 +14862,46 @@
         <v>458.43180265475399</v>
       </c>
       <c r="E73" t="s">
+        <v>109</v>
+      </c>
+      <c r="F73" t="s">
         <v>110</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>111</v>
       </c>
-      <c r="G73" t="s">
-        <v>112</v>
-      </c>
       <c r="H73" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>1174</v>
+        <v>1161</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>1291</v>
+        <v>1278</v>
       </c>
       <c r="S73">
         <v>13.854266764118</v>
@@ -14908,7 +14910,7 @@
         <v>460</v>
       </c>
       <c r="U73" s="7" t="s">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="V73">
         <v>14135.08</v>
@@ -15082,7 +15084,7 @@
         <v>57780.58</v>
       </c>
       <c r="CA73" t="s">
-        <v>1563</v>
+        <v>1488</v>
       </c>
       <c r="CB73">
         <v>37082778138.18</v>
@@ -15105,46 +15107,46 @@
         <v>466.99537424795102</v>
       </c>
       <c r="E74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F74" t="s">
+        <v>103</v>
+      </c>
+      <c r="G74" t="s">
         <v>104</v>
       </c>
-      <c r="G74" t="s">
-        <v>105</v>
-      </c>
       <c r="H74" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>1060</v>
+        <v>1048</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>1173</v>
+        <v>1160</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>1290</v>
+        <v>1277</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S74">
         <v>13.666362046130899</v>
@@ -15153,10 +15155,10 @@
         <v>461.5</v>
       </c>
       <c r="U74" s="7" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="CA74" t="s">
-        <v>1519</v>
+        <v>1444</v>
       </c>
       <c r="CB74">
         <v>36996157229.099998</v>
@@ -15177,46 +15179,46 @@
         <v>474.97478586918498</v>
       </c>
       <c r="E75" t="s">
+        <v>105</v>
+      </c>
+      <c r="F75" t="s">
         <v>106</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>107</v>
       </c>
-      <c r="G75" t="s">
-        <v>108</v>
-      </c>
       <c r="H75" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>1172</v>
+        <v>1159</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>1290</v>
+        <v>1277</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S75">
         <v>13.616159631618601</v>
@@ -15225,10 +15227,10 @@
         <v>460</v>
       </c>
       <c r="U75" s="7" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="CA75" t="s">
-        <v>1564</v>
+        <v>1489</v>
       </c>
       <c r="CB75">
         <v>36678837822.019997</v>
@@ -15249,46 +15251,46 @@
         <v>483.79242699340602</v>
       </c>
       <c r="E76" t="s">
+        <v>102</v>
+      </c>
+      <c r="F76" t="s">
         <v>103</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>104</v>
       </c>
-      <c r="G76" t="s">
-        <v>105</v>
-      </c>
       <c r="H76" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>1058</v>
+        <v>1046</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>1171</v>
+        <v>1158</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>1289</v>
+        <v>1276</v>
       </c>
       <c r="S76">
         <v>13.9740079468991</v>
@@ -15297,7 +15299,7 @@
         <v>461</v>
       </c>
       <c r="U76" s="7" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="V76">
         <v>10059.620000000001</v>
@@ -15471,7 +15473,7 @@
         <v>51947.19</v>
       </c>
       <c r="CA76" t="s">
-        <v>1520</v>
+        <v>1445</v>
       </c>
       <c r="CB76">
         <v>35497122764.580002</v>
@@ -15492,46 +15494,46 @@
         <v>493.03044447395803</v>
       </c>
       <c r="E77" t="s">
+        <v>100</v>
+      </c>
+      <c r="F77" t="s">
+        <v>48</v>
+      </c>
+      <c r="G77" t="s">
         <v>101</v>
       </c>
-      <c r="F77" t="s">
-        <v>49</v>
-      </c>
-      <c r="G77" t="s">
-        <v>102</v>
-      </c>
       <c r="H77" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>1170</v>
+        <v>1157</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>1288</v>
+        <v>1275</v>
       </c>
       <c r="S77">
         <v>14.0501151950509</v>
@@ -15540,10 +15542,10 @@
         <v>460.1</v>
       </c>
       <c r="U77" s="7" t="s">
-        <v>1408</v>
+        <v>1390</v>
       </c>
       <c r="CA77" t="s">
-        <v>1565</v>
+        <v>1490</v>
       </c>
       <c r="CB77">
         <v>35250914723.610001</v>
@@ -15564,46 +15566,46 @@
         <v>502.60464094475901</v>
       </c>
       <c r="E78" t="s">
+        <v>97</v>
+      </c>
+      <c r="F78" t="s">
         <v>98</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>99</v>
       </c>
-      <c r="G78" t="s">
-        <v>100</v>
-      </c>
       <c r="H78" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>1056</v>
+        <v>1044</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>1169</v>
+        <v>1156</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>1285</v>
+        <v>1272</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>1287</v>
+        <v>1274</v>
       </c>
       <c r="S78">
         <v>14.07</v>
@@ -15612,10 +15614,10 @@
         <v>466</v>
       </c>
       <c r="U78" s="7" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="CA78" t="s">
-        <v>1566</v>
+        <v>1491</v>
       </c>
       <c r="CB78">
         <v>35094421973.75</v>
@@ -15636,46 +15638,46 @@
         <v>513.30228441663701</v>
       </c>
       <c r="E79" t="s">
+        <v>94</v>
+      </c>
+      <c r="F79" t="s">
         <v>95</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>96</v>
       </c>
-      <c r="G79" t="s">
-        <v>97</v>
-      </c>
       <c r="H79" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>1055</v>
+        <v>1043</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>1168</v>
+        <v>1155</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>1285</v>
+        <v>1272</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>1286</v>
+        <v>1273</v>
       </c>
       <c r="S79">
         <v>13.85</v>
@@ -15684,7 +15686,7 @@
         <v>770.88</v>
       </c>
       <c r="U79" s="7" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="V79">
         <v>10980.38</v>
@@ -15858,7 +15860,7 @@
         <v>52755.88</v>
       </c>
       <c r="CA79" t="s">
-        <v>1521</v>
+        <v>1446</v>
       </c>
       <c r="CB79">
         <v>34119447985.860001</v>
@@ -15879,46 +15881,46 @@
         <v>528.11747341494799</v>
       </c>
       <c r="E80" t="s">
+        <v>92</v>
+      </c>
+      <c r="F80" t="s">
+        <v>56</v>
+      </c>
+      <c r="G80" t="s">
         <v>93</v>
       </c>
-      <c r="F80" t="s">
-        <v>57</v>
-      </c>
-      <c r="G80" t="s">
-        <v>94</v>
-      </c>
       <c r="H80" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>1054</v>
+        <v>1042</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>1167</v>
+        <v>1154</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>1284</v>
+        <v>1271</v>
       </c>
       <c r="S80">
         <v>13.98</v>
@@ -15927,10 +15929,10 @@
         <v>758.02200000000005</v>
       </c>
       <c r="U80" s="7" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="CA80" t="s">
-        <v>1567</v>
+        <v>1492</v>
       </c>
       <c r="CB80">
         <v>33952248666.810001</v>
@@ -15951,46 +15953,46 @@
         <v>544.90581833531496</v>
       </c>
       <c r="E81" t="s">
+        <v>89</v>
+      </c>
+      <c r="F81" t="s">
         <v>90</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>91</v>
       </c>
-      <c r="G81" t="s">
-        <v>92</v>
-      </c>
       <c r="H81" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>1166</v>
+        <v>1153</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>1283</v>
+        <v>1270</v>
       </c>
       <c r="S81">
         <v>13.99</v>
@@ -15999,10 +16001,10 @@
         <v>757.52</v>
       </c>
       <c r="U81" s="7" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="CA81" t="s">
-        <v>1522</v>
+        <v>1447</v>
       </c>
       <c r="CB81">
         <v>33954113883.810001</v>
@@ -16023,46 +16025,46 @@
         <v>556.33534985751101</v>
       </c>
       <c r="E82" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F82" t="s">
+        <v>68</v>
+      </c>
+      <c r="G82" t="s">
         <v>69</v>
       </c>
-      <c r="G82" t="s">
-        <v>70</v>
-      </c>
       <c r="H82" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>1052</v>
+        <v>1040</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>1282</v>
+        <v>1269</v>
       </c>
       <c r="S82">
         <v>14.32</v>
@@ -16071,7 +16073,7 @@
         <v>769.26</v>
       </c>
       <c r="U82" s="7" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="V82">
         <v>15986.82</v>
@@ -16245,7 +16247,7 @@
         <v>62054.36</v>
       </c>
       <c r="CA82" t="s">
-        <v>1568</v>
+        <v>1493</v>
       </c>
       <c r="CB82">
         <v>33237603572.34</v>
@@ -16266,46 +16268,46 @@
         <v>565.98490876641802</v>
       </c>
       <c r="E83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F83" t="s">
+        <v>68</v>
+      </c>
+      <c r="G83" t="s">
         <v>69</v>
       </c>
-      <c r="G83" t="s">
-        <v>70</v>
-      </c>
       <c r="H83" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>1051</v>
+        <v>1039</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>1164</v>
+        <v>1151</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>1281</v>
+        <v>1268</v>
       </c>
       <c r="S83">
         <v>14.39</v>
@@ -16314,10 +16316,10 @@
         <v>825.49</v>
       </c>
       <c r="U83" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="CA83" t="s">
-        <v>1523</v>
+        <v>1448</v>
       </c>
       <c r="CB83">
         <v>33396135968.560001</v>
@@ -16338,46 +16340,46 @@
         <v>577.80238355587301</v>
       </c>
       <c r="E84" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F84" t="s">
+        <v>75</v>
+      </c>
+      <c r="G84" t="s">
         <v>76</v>
       </c>
-      <c r="G84" t="s">
-        <v>77</v>
-      </c>
       <c r="H84" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>1050</v>
+        <v>1038</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>1163</v>
+        <v>1150</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>1280</v>
+        <v>1267</v>
       </c>
       <c r="S84">
         <v>14.05</v>
@@ -16386,10 +16388,10 @@
         <v>942.61699999999996</v>
       </c>
       <c r="U84" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="CA84" t="s">
-        <v>1524</v>
+        <v>1449</v>
       </c>
       <c r="CB84">
         <v>33004054737.400002</v>
@@ -16410,46 +16412,46 @@
         <v>591.01848501080497</v>
       </c>
       <c r="E85" t="s">
+        <v>83</v>
+      </c>
+      <c r="F85" t="s">
         <v>84</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>85</v>
       </c>
-      <c r="G85" t="s">
-        <v>86</v>
-      </c>
       <c r="H85" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>1162</v>
+        <v>1149</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>1279</v>
+        <v>1266</v>
       </c>
       <c r="S85">
         <v>14.17</v>
@@ -16458,7 +16460,7 @@
         <v>899.89300000000003</v>
       </c>
       <c r="U85" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="V85">
         <v>16246.32</v>
@@ -16632,7 +16634,7 @@
         <v>67668.479999999996</v>
       </c>
       <c r="CA85" t="s">
-        <v>1569</v>
+        <v>1494</v>
       </c>
       <c r="CB85">
         <v>32912429900.169998</v>
@@ -16655,46 +16657,46 @@
         <v>606.62259550188901</v>
       </c>
       <c r="E86" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F86" t="s">
+        <v>40</v>
+      </c>
+      <c r="G86" t="s">
         <v>41</v>
       </c>
-      <c r="G86" t="s">
-        <v>42</v>
-      </c>
       <c r="H86" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>1048</v>
+        <v>1036</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>1161</v>
+        <v>1148</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>1278</v>
+        <v>1265</v>
       </c>
       <c r="S86">
         <v>13.82</v>
@@ -16703,10 +16705,10 @@
         <v>1357.383</v>
       </c>
       <c r="U86" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="CA86" t="s">
-        <v>1569</v>
+        <v>1494</v>
       </c>
       <c r="CB86">
         <v>32912429900.169998</v>
@@ -16727,46 +16729,46 @@
         <v>625.53339763153394</v>
       </c>
       <c r="E87" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F87" t="s">
+        <v>65</v>
+      </c>
+      <c r="G87" t="s">
         <v>66</v>
       </c>
-      <c r="G87" t="s">
-        <v>67</v>
-      </c>
       <c r="H87" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>1275</v>
+        <v>1262</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>1276</v>
+        <v>1263</v>
       </c>
       <c r="S87">
         <v>15.06</v>
@@ -16775,10 +16777,10 @@
         <v>1544.5809999999999</v>
       </c>
       <c r="U87" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="CA87" t="s">
-        <v>1570</v>
+        <v>1495</v>
       </c>
       <c r="CB87">
         <v>33353665926.860001</v>
@@ -16799,46 +16801,46 @@
         <v>644.41844390948597</v>
       </c>
       <c r="E88" t="s">
+        <v>78</v>
+      </c>
+      <c r="F88" t="s">
         <v>79</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>80</v>
       </c>
-      <c r="G88" t="s">
-        <v>81</v>
-      </c>
       <c r="H88" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>1046</v>
+        <v>1034</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>1159</v>
+        <v>1146</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>1272</v>
+        <v>1259</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>1274</v>
+        <v>1261</v>
       </c>
       <c r="S88">
         <v>15.7</v>
@@ -16847,7 +16849,7 @@
         <v>1330.76</v>
       </c>
       <c r="U88" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="V88">
         <v>10137.040000000001</v>
@@ -17021,7 +17023,7 @@
         <v>60276.87</v>
       </c>
       <c r="CA88" t="s">
-        <v>1525</v>
+        <v>1450</v>
       </c>
       <c r="CB88">
         <v>33718605623.130001</v>
@@ -17042,46 +17044,46 @@
         <v>659.15540264571496</v>
       </c>
       <c r="E89" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F89" t="s">
+        <v>72</v>
+      </c>
+      <c r="G89" t="s">
         <v>73</v>
       </c>
-      <c r="G89" t="s">
-        <v>74</v>
-      </c>
       <c r="H89" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>1158</v>
+        <v>1145</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>1272</v>
+        <v>1259</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>1273</v>
+        <v>1260</v>
       </c>
       <c r="S89">
         <v>15.54</v>
@@ -17090,10 +17092,10 @@
         <v>1330.2049999999999</v>
       </c>
       <c r="U89" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="CA89" t="s">
-        <v>1571</v>
+        <v>1496</v>
       </c>
       <c r="CB89">
         <v>33827356277.139999</v>
@@ -17114,46 +17116,46 @@
         <v>673.25406683375297</v>
       </c>
       <c r="E90" t="s">
+        <v>74</v>
+      </c>
+      <c r="F90" t="s">
         <v>75</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>76</v>
       </c>
-      <c r="G90" t="s">
-        <v>77</v>
-      </c>
       <c r="H90" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>1044</v>
+        <v>1032</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>1157</v>
+        <v>1144</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>1270</v>
+        <v>1257</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="S90">
         <v>15.54</v>
@@ -17162,10 +17164,10 @@
         <v>1483.482</v>
       </c>
       <c r="U90" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="CA90" t="s">
-        <v>1526</v>
+        <v>1451</v>
       </c>
       <c r="CB90">
         <v>32254525124.299999</v>
@@ -17186,46 +17188,46 @@
         <v>688.808915537193</v>
       </c>
       <c r="E91" t="s">
+        <v>71</v>
+      </c>
+      <c r="F91" t="s">
         <v>72</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>73</v>
       </c>
-      <c r="G91" t="s">
-        <v>74</v>
-      </c>
       <c r="H91" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>1156</v>
+        <v>1143</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>1270</v>
+        <v>1257</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>1271</v>
+        <v>1258</v>
       </c>
       <c r="S91">
         <v>15.85</v>
@@ -17234,7 +17236,7 @@
         <v>1470.691</v>
       </c>
       <c r="U91" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="V91">
         <v>11293.99</v>
@@ -17408,7 +17410,7 @@
         <v>62232.72</v>
       </c>
       <c r="CA91" t="s">
-        <v>1527</v>
+        <v>1452</v>
       </c>
       <c r="CB91">
         <v>32694681787.23</v>
@@ -17429,46 +17431,46 @@
         <v>704.48363394650801</v>
       </c>
       <c r="E92" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F92" t="s">
+        <v>25</v>
+      </c>
+      <c r="G92" t="s">
         <v>26</v>
       </c>
-      <c r="G92" t="s">
-        <v>27</v>
-      </c>
       <c r="H92" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>1155</v>
+        <v>1142</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>1267</v>
+        <v>1254</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>1269</v>
+        <v>1256</v>
       </c>
       <c r="S92">
         <v>15.89</v>
@@ -17477,10 +17479,10 @@
         <v>1611.71</v>
       </c>
       <c r="U92" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="CA92" t="s">
-        <v>1572</v>
+        <v>1497</v>
       </c>
       <c r="CB92">
         <v>34191523805.75</v>
@@ -17501,46 +17503,46 @@
         <v>720.09375981685696</v>
       </c>
       <c r="E93" t="s">
+        <v>67</v>
+      </c>
+      <c r="F93" t="s">
         <v>68</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>69</v>
       </c>
-      <c r="G93" t="s">
-        <v>70</v>
-      </c>
       <c r="H93" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>1041</v>
+        <v>1029</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>1154</v>
+        <v>1141</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>1267</v>
+        <v>1254</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>1268</v>
+        <v>1255</v>
       </c>
       <c r="S93">
         <v>17.010000000000002</v>
@@ -17549,10 +17551,10 @@
         <v>1596.64</v>
       </c>
       <c r="U93" s="7" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="CA93" t="s">
-        <v>1528</v>
+        <v>1453</v>
       </c>
       <c r="CB93">
         <v>36797462436.279999</v>
@@ -17573,46 +17575,46 @@
         <v>738.23629005582495</v>
       </c>
       <c r="E94" t="s">
+        <v>64</v>
+      </c>
+      <c r="F94" t="s">
         <v>65</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>66</v>
       </c>
-      <c r="G94" t="s">
-        <v>67</v>
-      </c>
       <c r="H94" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>1040</v>
+        <v>1028</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>1153</v>
+        <v>1140</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>1264</v>
+        <v>1251</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>1266</v>
+        <v>1253</v>
       </c>
       <c r="S94">
         <v>16.75</v>
@@ -17621,7 +17623,7 @@
         <v>1601.53</v>
       </c>
       <c r="U94" s="7" t="s">
-        <v>1411</v>
+        <v>1393</v>
       </c>
       <c r="V94">
         <v>17791.72</v>
@@ -17795,7 +17797,7 @@
         <v>73755.08</v>
       </c>
       <c r="CA94" t="s">
-        <v>1573</v>
+        <v>1498</v>
       </c>
       <c r="CB94">
         <v>36305654424.25</v>
@@ -17816,46 +17818,46 @@
         <v>757.72289362402501</v>
       </c>
       <c r="E95" t="s">
+        <v>61</v>
+      </c>
+      <c r="F95" t="s">
         <v>62</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
         <v>63</v>
       </c>
-      <c r="G95" t="s">
-        <v>64</v>
-      </c>
       <c r="H95" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>1039</v>
+        <v>1027</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>1152</v>
+        <v>1139</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>1264</v>
+        <v>1251</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>1265</v>
+        <v>1252</v>
       </c>
       <c r="S95">
         <v>17.3583437362796</v>
@@ -17867,7 +17869,7 @@
         <v>1184.8254225255844</v>
       </c>
       <c r="CA95" t="s">
-        <v>1529</v>
+        <v>1454</v>
       </c>
       <c r="CB95">
         <v>38352539980.610001</v>
@@ -17888,46 +17890,46 @@
         <v>777.71238001215499</v>
       </c>
       <c r="E96" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F96" t="s">
+        <v>19</v>
+      </c>
+      <c r="G96" t="s">
         <v>20</v>
       </c>
-      <c r="G96" t="s">
-        <v>21</v>
-      </c>
       <c r="H96" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>1038</v>
+        <v>1026</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>1151</v>
+        <v>1138</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="S96">
         <v>18.393732487518001</v>
@@ -17939,7 +17941,7 @@
         <v>1214.1674524908103</v>
       </c>
       <c r="CA96" t="s">
-        <v>1530</v>
+        <v>1455</v>
       </c>
       <c r="CB96">
         <v>39785523194.43</v>
@@ -17960,46 +17962,46 @@
         <v>796.66961655827799</v>
       </c>
       <c r="E97" t="s">
+        <v>57</v>
+      </c>
+      <c r="F97" t="s">
         <v>58</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>59</v>
       </c>
-      <c r="G97" t="s">
-        <v>60</v>
-      </c>
       <c r="H97" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>1037</v>
+        <v>1025</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>1150</v>
+        <v>1137</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="S97">
         <v>18.562820885048598</v>
@@ -18182,7 +18184,7 @@
         <v>81229.11</v>
       </c>
       <c r="CA97" t="s">
-        <v>1574</v>
+        <v>1499</v>
       </c>
       <c r="CB97">
         <v>40232463200.199997</v>
@@ -18205,46 +18207,46 @@
         <v>774.08774776448604</v>
       </c>
       <c r="E98" t="s">
+        <v>54</v>
+      </c>
+      <c r="F98" t="s">
         <v>55</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>56</v>
       </c>
-      <c r="G98" t="s">
-        <v>57</v>
-      </c>
       <c r="H98" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>1149</v>
+        <v>1136</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
       <c r="R98" s="2" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="S98">
         <v>18.493996259713199</v>
@@ -18256,7 +18258,7 @@
         <v>1258.3446139544001</v>
       </c>
       <c r="CA98" t="s">
-        <v>1531</v>
+        <v>1456</v>
       </c>
       <c r="CB98">
         <v>40877997438.449997</v>
@@ -18277,46 +18279,46 @@
         <v>789.888635570612</v>
       </c>
       <c r="E99" t="s">
+        <v>51</v>
+      </c>
+      <c r="F99" t="s">
         <v>52</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>53</v>
       </c>
-      <c r="G99" t="s">
-        <v>54</v>
-      </c>
       <c r="H99" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>1035</v>
+        <v>1023</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>1148</v>
+        <v>1135</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
       <c r="R99" s="2" t="s">
-        <v>1262</v>
+        <v>1249</v>
       </c>
       <c r="S99">
         <v>18.347533104431999</v>
@@ -18328,7 +18330,7 @@
         <v>1245.80113436542</v>
       </c>
       <c r="CA99" t="s">
-        <v>1532</v>
+        <v>1457</v>
       </c>
       <c r="CB99">
         <v>39723161364.779999</v>
@@ -18349,46 +18351,46 @@
         <v>820.65700095338002</v>
       </c>
       <c r="E100" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F100" t="s">
+        <v>34</v>
+      </c>
+      <c r="G100" t="s">
         <v>35</v>
       </c>
-      <c r="G100" t="s">
-        <v>36</v>
-      </c>
       <c r="H100" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>1034</v>
+        <v>1022</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>1147</v>
+        <v>1134</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
       <c r="R100" s="2" t="s">
-        <v>1261</v>
+        <v>1248</v>
       </c>
       <c r="S100">
         <v>17.955375893521801</v>
@@ -18571,7 +18573,7 @@
         <v>96102.440892054175</v>
       </c>
       <c r="CA100" t="s">
-        <v>1533</v>
+        <v>1458</v>
       </c>
       <c r="CB100">
         <v>38416382169.389999</v>
@@ -18592,46 +18594,46 @@
         <v>835.91405504889201</v>
       </c>
       <c r="E101" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F101" t="s">
+        <v>19</v>
+      </c>
+      <c r="G101" t="s">
         <v>20</v>
       </c>
-      <c r="G101" t="s">
-        <v>21</v>
-      </c>
       <c r="H101" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>1033</v>
+        <v>1021</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>1146</v>
+        <v>1133</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
       <c r="R101" s="2" t="s">
-        <v>1260</v>
+        <v>1247</v>
       </c>
       <c r="S101">
         <v>18.323877234482001</v>
@@ -18643,7 +18645,7 @@
         <v>1239.3271114285071</v>
       </c>
       <c r="CA101" t="s">
-        <v>1575</v>
+        <v>1500</v>
       </c>
       <c r="CB101">
         <v>38308209720.169998</v>
@@ -18664,46 +18666,46 @@
         <v>848.71293992790402</v>
       </c>
       <c r="E102" t="s">
+        <v>46</v>
+      </c>
+      <c r="F102" t="s">
         <v>47</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>48</v>
       </c>
-      <c r="G102" t="s">
-        <v>49</v>
-      </c>
       <c r="H102" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>1032</v>
+        <v>1020</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>1145</v>
+        <v>1132</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
       <c r="R102" s="2" t="s">
-        <v>1259</v>
+        <v>1246</v>
       </c>
       <c r="S102">
         <v>18.0113258732726</v>
@@ -18715,7 +18717,7 @@
         <v>1027.7573777589457</v>
       </c>
       <c r="CA102" t="s">
-        <v>1534</v>
+        <v>1459</v>
       </c>
       <c r="CB102">
         <v>37933500695.059998</v>
@@ -18736,46 +18738,46 @@
         <v>862.98568983695804</v>
       </c>
       <c r="E103" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F103" t="s">
+        <v>43</v>
+      </c>
+      <c r="G103" t="s">
         <v>44</v>
       </c>
-      <c r="G103" t="s">
-        <v>45</v>
-      </c>
       <c r="H103" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>1031</v>
+        <v>1019</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>1144</v>
+        <v>1131</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
       <c r="R103" s="2" t="s">
-        <v>1258</v>
+        <v>1245</v>
       </c>
       <c r="S103">
         <v>18.194997566233098</v>
@@ -18958,7 +18960,7 @@
         <v>102452.07033048211</v>
       </c>
       <c r="CA103" t="s">
-        <v>1576</v>
+        <v>1501</v>
       </c>
       <c r="CB103">
         <v>38448383517.739998</v>
@@ -18979,46 +18981,46 @@
         <v>880.18560766317796</v>
       </c>
       <c r="E104" t="s">
+        <v>42</v>
+      </c>
+      <c r="F104" t="s">
         <v>43</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>44</v>
       </c>
-      <c r="G104" t="s">
-        <v>45</v>
-      </c>
       <c r="H104" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>1143</v>
+        <v>1130</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
       <c r="R104" s="2" t="s">
-        <v>1257</v>
+        <v>1244</v>
       </c>
       <c r="S104">
         <v>18.536546119556199</v>
@@ -19030,7 +19032,7 @@
         <v>1024.9930062617211</v>
       </c>
       <c r="CA104" t="s">
-        <v>1535</v>
+        <v>1460</v>
       </c>
       <c r="CB104">
         <v>37210889172.989998</v>
@@ -19051,46 +19053,46 @@
         <v>886.73534957593597</v>
       </c>
       <c r="E105" t="s">
+        <v>39</v>
+      </c>
+      <c r="F105" t="s">
         <v>40</v>
       </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>41</v>
       </c>
-      <c r="G105" t="s">
-        <v>42</v>
-      </c>
       <c r="H105" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>1142</v>
+        <v>1129</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>1249</v>
+        <v>1236</v>
       </c>
       <c r="R105" s="2" t="s">
-        <v>1255</v>
+        <v>1242</v>
       </c>
       <c r="S105">
         <v>18.8839341244779</v>
@@ -19102,7 +19104,7 @@
         <v>988.25338049867639</v>
       </c>
       <c r="CA105" t="s">
-        <v>1577</v>
+        <v>1502</v>
       </c>
       <c r="CB105">
         <v>39359322066.32</v>
@@ -19123,46 +19125,46 @@
         <v>893.12437106545804</v>
       </c>
       <c r="E106" t="s">
+        <v>36</v>
+      </c>
+      <c r="F106" t="s">
         <v>37</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>38</v>
       </c>
-      <c r="G106" t="s">
-        <v>39</v>
-      </c>
       <c r="H106" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>1028</v>
+        <v>1016</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>1141</v>
+        <v>1128</v>
       </c>
       <c r="Q106" s="2" t="s">
-        <v>1249</v>
+        <v>1236</v>
       </c>
       <c r="R106" s="2" t="s">
-        <v>1254</v>
+        <v>1241</v>
       </c>
       <c r="S106">
         <v>18.897052571530299</v>
@@ -19345,7 +19347,7 @@
         <v>116948.630998051</v>
       </c>
       <c r="CA106" t="s">
-        <v>1578</v>
+        <v>1503</v>
       </c>
       <c r="CB106">
         <v>41305527591.440002</v>
@@ -19366,46 +19368,46 @@
         <v>901.517082461531</v>
       </c>
       <c r="E107" t="s">
+        <v>33</v>
+      </c>
+      <c r="F107" t="s">
         <v>34</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>35</v>
       </c>
-      <c r="G107" t="s">
-        <v>36</v>
-      </c>
       <c r="H107" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>1140</v>
+        <v>1127</v>
       </c>
       <c r="Q107" s="2" t="s">
-        <v>1249</v>
+        <v>1236</v>
       </c>
       <c r="R107" s="2" t="s">
-        <v>1253</v>
+        <v>1240</v>
       </c>
       <c r="S107">
         <v>18.8913816600441</v>
@@ -19417,7 +19419,7 @@
         <v>1052.311547273941</v>
       </c>
       <c r="CA107" t="s">
-        <v>1536</v>
+        <v>1461</v>
       </c>
       <c r="CB107">
         <v>42353924827.449997</v>
@@ -19438,46 +19440,46 @@
         <v>912.70736432296201</v>
       </c>
       <c r="E108" t="s">
+        <v>30</v>
+      </c>
+      <c r="F108" t="s">
         <v>31</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>32</v>
       </c>
-      <c r="G108" t="s">
-        <v>33</v>
-      </c>
       <c r="H108" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>1139</v>
+        <v>1126</v>
       </c>
       <c r="Q108" s="2" t="s">
-        <v>1249</v>
+        <v>1236</v>
       </c>
       <c r="R108" s="2" t="s">
-        <v>1252</v>
+        <v>1239</v>
       </c>
       <c r="S108">
         <v>18.885400305305701</v>
@@ -19489,7 +19491,7 @@
         <v>1061.3500169049423</v>
       </c>
       <c r="CA108" t="s">
-        <v>1537</v>
+        <v>1462</v>
       </c>
       <c r="CB108">
         <v>43197508512.669998</v>
@@ -19510,46 +19512,46 @@
         <v>917.36881611086505</v>
       </c>
       <c r="E109" t="s">
+        <v>27</v>
+      </c>
+      <c r="F109" t="s">
         <v>28</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>29</v>
       </c>
-      <c r="G109" t="s">
-        <v>30</v>
-      </c>
       <c r="H109" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>1138</v>
+        <v>1125</v>
       </c>
       <c r="Q109" s="2" t="s">
-        <v>1249</v>
+        <v>1236</v>
       </c>
       <c r="R109" s="2" t="s">
-        <v>1251</v>
+        <v>1238</v>
       </c>
       <c r="S109">
         <v>18.021189721181099</v>
@@ -19732,7 +19734,7 @@
         <v>126032.26758897699</v>
       </c>
       <c r="CA109" t="s">
-        <v>1579</v>
+        <v>1504</v>
       </c>
       <c r="CB109">
         <v>44668271689.410004</v>
@@ -19755,46 +19757,46 @@
         <v>890.95625395480602</v>
       </c>
       <c r="E110" t="s">
+        <v>27</v>
+      </c>
+      <c r="F110" t="s">
         <v>28</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>29</v>
       </c>
-      <c r="G110" t="s">
-        <v>30</v>
-      </c>
       <c r="H110" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>1137</v>
+        <v>1124</v>
       </c>
       <c r="Q110" s="2" t="s">
-        <v>1249</v>
+        <v>1236</v>
       </c>
       <c r="R110" s="2" t="s">
-        <v>1250</v>
+        <v>1237</v>
       </c>
       <c r="S110">
         <v>19.538309793458801</v>
@@ -19806,7 +19808,7 @@
         <v>1034.76</v>
       </c>
       <c r="CA110" t="s">
-        <v>1538</v>
+        <v>1463</v>
       </c>
       <c r="CB110">
         <v>45502438609.739998</v>
@@ -19827,46 +19829,46 @@
         <v>908.86070493309501</v>
       </c>
       <c r="E111" t="s">
+        <v>24</v>
+      </c>
+      <c r="F111" t="s">
         <v>25</v>
       </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>26</v>
       </c>
-      <c r="G111" t="s">
-        <v>27</v>
-      </c>
       <c r="H111" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="P111" s="2" t="s">
-        <v>1136</v>
+        <v>1123</v>
       </c>
       <c r="Q111" s="2" t="s">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="R111" s="2" t="s">
-        <v>1248</v>
+        <v>1235</v>
       </c>
       <c r="S111">
         <v>19.290214560836102</v>
@@ -19878,7 +19880,7 @@
         <v>1051.47</v>
       </c>
       <c r="CA111" t="s">
-        <v>1580</v>
+        <v>1505</v>
       </c>
       <c r="CB111">
         <v>46279901472.260002</v>
@@ -19899,46 +19901,46 @@
         <v>946.86962329755795</v>
       </c>
       <c r="E112" t="s">
+        <v>21</v>
+      </c>
+      <c r="F112" t="s">
         <v>22</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>23</v>
       </c>
-      <c r="G112" t="s">
-        <v>24</v>
-      </c>
       <c r="H112" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>1135</v>
+        <v>1122</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="R112" s="2" t="s">
-        <v>1247</v>
+        <v>1234</v>
       </c>
       <c r="S112">
         <v>19.290214560836102</v>
@@ -20121,7 +20123,7 @@
         <v>113186.87012029301</v>
       </c>
       <c r="CA112" t="s">
-        <v>1581</v>
+        <v>1506</v>
       </c>
       <c r="CB112">
         <v>49693978529.919998</v>
@@ -20142,46 +20144,46 @@
         <v>967.05017061253602</v>
       </c>
       <c r="E113" t="s">
+        <v>18</v>
+      </c>
+      <c r="F113" t="s">
         <v>19</v>
       </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
         <v>20</v>
       </c>
-      <c r="G113" t="s">
-        <v>21</v>
-      </c>
       <c r="H113" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>1135</v>
+        <v>1122</v>
       </c>
       <c r="Q113" s="2" t="s">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="R113" s="2" t="s">
-        <v>1247</v>
+        <v>1234</v>
       </c>
       <c r="S113">
         <v>18.8668901890738</v>
@@ -20193,7 +20195,7 @@
         <v>1532.9262169189903</v>
       </c>
       <c r="CA113" t="s">
-        <v>1539</v>
+        <v>1464</v>
       </c>
       <c r="CB113">
         <v>49238455590.699997</v>
@@ -20214,49 +20216,49 @@
         <v>983.93201866469701</v>
       </c>
       <c r="E114" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" t="s">
         <v>16</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>17</v>
       </c>
-      <c r="G114" t="s">
-        <v>18</v>
-      </c>
       <c r="H114" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>1021</v>
+        <v>1009</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>1134</v>
+        <v>1121</v>
       </c>
       <c r="Q114" s="2" t="s">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="R114" s="2" t="s">
-        <v>1247</v>
+        <v>1234</v>
       </c>
       <c r="S114" s="6" t="s">
-        <v>1347</v>
+        <v>1331</v>
       </c>
       <c r="T114">
         <v>1373.2545</v>
@@ -20265,7 +20267,7 @@
         <v>1596.2458192931645</v>
       </c>
       <c r="CA114" t="s">
-        <v>1540</v>
+        <v>1465</v>
       </c>
       <c r="CB114">
         <v>48364008532.760002</v>
@@ -20283,10 +20285,10 @@
         <v>6</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="CA115" t="s">
-        <v>1582</v>
+        <v>1507</v>
       </c>
       <c r="CB115">
         <v>49580970779.290001</v>
@@ -20304,7 +20306,7 @@
         <v>7</v>
       </c>
       <c r="CA116" t="s">
-        <v>1541</v>
+        <v>1466</v>
       </c>
       <c r="CB116">
         <v>51459234516.220001</v>
@@ -20322,7 +20324,7 @@
         <v>8</v>
       </c>
       <c r="CA117" t="s">
-        <v>1583</v>
+        <v>1508</v>
       </c>
       <c r="CB117">
         <v>51915644681.029999</v>
